--- a/cnn results/cnn result - epsilon.xlsx
+++ b/cnn results/cnn result - epsilon.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\flight delay\stpn paper\STPN-main\cnn results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDC80E2-6097-42A1-9A40-D5F52F7CF77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1454E7FB-1C95-4AAE-B9D5-8A55CB95BD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7584" yWindow="0" windowWidth="12336" windowHeight="11448" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId2"/>
+    <sheet name="udata " sheetId="8" r:id="rId2"/>
+    <sheet name="cdata epsilon" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="87">
   <si>
     <t>classification_precision</t>
   </si>
@@ -44,9 +45,6 @@
   </si>
   <si>
     <t>regression_rmse_delayed</t>
-  </si>
-  <si>
-    <t>regression_mae_nondelayed</t>
   </si>
   <si>
     <t>regression_rmse_nondelayed</t>
@@ -156,12 +154,147 @@
   <si>
     <t>2037.683 - approx</t>
   </si>
+  <si>
+    <t>Run Tag</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>Final ε</t>
+  </si>
+  <si>
+    <t>Overall MAE</t>
+  </si>
+  <si>
+    <t>Arr MAE</t>
+  </si>
+  <si>
+    <t>Dep MAE</t>
+  </si>
+  <si>
+    <t>Arr MAE Delayed</t>
+  </si>
+  <si>
+    <t>Dep MAE Delayed</t>
+  </si>
+  <si>
+    <t>Arr MAE Non-delayed</t>
+  </si>
+  <si>
+    <t>Dep MAE Non-delayed</t>
+  </si>
+  <si>
+    <t>cnnopacus_udata_sigma0_00</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>cnnopacus_udata_sigma0_71</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>cnnopacus_udata_sigma0_34</t>
+  </si>
+  <si>
+    <t>cnnopacus_udata_sigma0_33</t>
+  </si>
+  <si>
+    <t>cnnopacus_udata_sigma0_31</t>
+  </si>
+  <si>
+    <t>Sigma</t>
+  </si>
+  <si>
+    <t>DP Enabled</t>
+  </si>
+  <si>
+    <t>Target Epsilon</t>
+  </si>
+  <si>
+    <t>Final Epsilon</t>
+  </si>
+  <si>
+    <t>Arrival MAE</t>
+  </si>
+  <si>
+    <t>Departure MAE</t>
+  </si>
+  <si>
+    <t>Precision</t>
+  </si>
+  <si>
+    <t>Recall</t>
+  </si>
+  <si>
+    <t>F1 Score</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>MAE Del Arr</t>
+  </si>
+  <si>
+    <t>MAE Del Dep</t>
+  </si>
+  <si>
+    <t>MAE NonDel Arr</t>
+  </si>
+  <si>
+    <t>MAE NonDel Dep</t>
+  </si>
+  <si>
+    <t>Arrival MAE delayed</t>
+  </si>
+  <si>
+    <t>ep</t>
+  </si>
+  <si>
+    <t>Departure MAE delayed</t>
+  </si>
+  <si>
+    <t>Arrival MAE non del</t>
+  </si>
+  <si>
+    <t>Departure MAE non del</t>
+  </si>
+  <si>
+    <t>Overall MAE (min)</t>
+  </si>
+  <si>
+    <t>Arrival MAE (min)</t>
+  </si>
+  <si>
+    <t>Departure MAE (min)</t>
+  </si>
+  <si>
+    <t>regression_mae_ nondelayed</t>
+  </si>
+  <si>
+    <t>cnnopacus_udata_sigma0_37</t>
+  </si>
+  <si>
+    <t>cnnopacus_cdata_sigma0_38 (115614)</t>
+  </si>
+  <si>
+    <t>cnnopacus_cdata_sigma0_38 (121259)</t>
+  </si>
+  <si>
+    <t>Run Tag (Timestamp) threshold change</t>
+  </si>
+  <si>
+    <t>threshold</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,6 +314,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -224,13 +365,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -264,6 +412,14 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.31207080646206459"/>
+          <c:y val="2.8376643713363129E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -304,7 +460,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$1</c:f>
+              <c:f>Sheet1!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -339,7 +495,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$5</c:f>
+              <c:f>Sheet1!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -360,7 +516,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$2:$I$5</c:f>
+              <c:f>Sheet1!$E$2:$E$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -407,14 +563,14 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$J$1</c15:sqref>
+                          <c15:sqref>Sheet1!$F$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>regression_mae_nondelayed</c:v>
+                        <c:v>regression_mae_ nondelayed</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -448,7 +604,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$F$2:$F$5</c15:sqref>
+                          <c15:sqref>Sheet1!$B$2:$B$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -475,7 +631,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$J$2:$J$5</c15:sqref>
+                          <c15:sqref>Sheet1!$F$2:$F$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -514,7 +670,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$K$1</c15:sqref>
+                          <c15:sqref>Sheet1!$G$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -555,7 +711,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$F$2:$F$5</c15:sqref>
+                          <c15:sqref>Sheet1!$B$2:$B$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -582,7 +738,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$K$2:$K$5</c15:sqref>
+                          <c15:sqref>Sheet1!$G$2:$G$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -877,11 +1033,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$J$1</c:f>
+              <c:f>Sheet1!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>regression_mae_nondelayed</c:v>
+                  <c:v>regression_mae_ nondelayed</c:v>
                 </c:pt>
               </c:strCache>
               <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
@@ -913,7 +1069,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$5</c:f>
+              <c:f>Sheet1!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -935,7 +1091,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$J$2:$J$5</c:f>
+              <c:f>Sheet1!$F$2:$F$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -983,7 +1139,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$I$1</c15:sqref>
+                          <c15:sqref>Sheet1!$E$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1024,7 +1180,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$F$2:$F$5</c15:sqref>
+                          <c15:sqref>Sheet1!$B$2:$B$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1051,7 +1207,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$I$2:$I$5</c15:sqref>
+                          <c15:sqref>Sheet1!$E$2:$E$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1090,7 +1246,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$K$1</c15:sqref>
+                          <c15:sqref>Sheet1!$G$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1131,7 +1287,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$F$2:$F$5</c15:sqref>
+                          <c15:sqref>Sheet1!$B$2:$B$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1158,7 +1314,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$K$2:$K$5</c15:sqref>
+                          <c15:sqref>Sheet1!$G$2:$G$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1453,7 +1609,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$K$1</c:f>
+              <c:f>Sheet1!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1489,7 +1645,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$5</c:f>
+              <c:f>Sheet1!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1511,7 +1667,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$K$2:$K$5</c:f>
+              <c:f>Sheet1!$G$2:$G$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1559,7 +1715,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$I$1</c15:sqref>
+                          <c15:sqref>Sheet1!$E$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1600,7 +1756,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$F$2:$F$5</c15:sqref>
+                          <c15:sqref>Sheet1!$B$2:$B$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1627,7 +1783,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$I$2:$I$5</c15:sqref>
+                          <c15:sqref>Sheet1!$E$2:$E$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1666,14 +1822,14 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$J$1</c15:sqref>
+                          <c15:sqref>Sheet1!$F$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>regression_mae_nondelayed</c:v>
+                        <c:v>regression_mae_ nondelayed</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -1707,7 +1863,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$F$2:$F$5</c15:sqref>
+                          <c15:sqref>Sheet1!$B$2:$B$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1734,7 +1890,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$J$2:$J$5</c15:sqref>
+                          <c15:sqref>Sheet1!$F$2:$F$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1989,6 +2145,1332 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MAE Delayed</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'udata '!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Arr MAE Delayed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'udata '!$C$2:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.99150000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5340000000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.994199999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.6371</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'udata '!$G$2:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10.796200000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.3282000000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.8496000000000006</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.7787000000000006</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.6802999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FF4E-4AEF-8DF1-BC3554EF1067}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="258195152"/>
+        <c:axId val="258193072"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="258195152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="258193072"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="258193072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="258195152"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'udata '!$I$44</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Precision</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'udata '!$E$45:$E$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.99150000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.994</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.329000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.637</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'udata '!$I$45:$I$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.35549999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2782</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2777</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.27310000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-558A-4B50-B9AD-D2FD8F7B60DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'udata '!$J$44</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Recall</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'udata '!$E$45:$E$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.99150000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.994</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.329000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.637</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'udata '!$J$45:$J$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.2356</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.58360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.59060000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.60509999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-558A-4B50-B9AD-D2FD8F7B60DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'udata '!$K$44</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>F1 Score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'udata '!$E$45:$E$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.99150000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.994</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.329000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.637</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'udata '!$K$45:$K$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.28289999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.37640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.3765</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.37630000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-558A-4B50-B9AD-D2FD8F7B60DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'udata '!$L$44</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'udata '!$E$45:$E$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.99150000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.994</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.329000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.637</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'udata '!$L$45:$L$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.78269999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.64970000000000006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.64459999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.63639999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-558A-4B50-B9AD-D2FD8F7B60DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="436327792"/>
+        <c:axId val="436328208"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="436327792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="436328208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="436328208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="436327792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Dep MAE overall</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'udata '!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Dep MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'udata '!$C$2:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.99150000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5340000000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.994199999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.6371</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'udata '!$F$2:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3.9706999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7098000000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.2220000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.516</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.8971999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AF5A-4D3C-902D-8EF16937614B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="70020448"/>
+        <c:axId val="70017120"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="70020448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="70017120"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="70017120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="70020448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2029,7 +3511,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$I$1</c:f>
+              <c:f>'cdata epsilon'!$I$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2064,7 +3546,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$B$2:$B$5</c:f>
+              <c:f>'cdata epsilon'!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2085,7 +3567,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$I$2:$I$5</c:f>
+              <c:f>'cdata epsilon'!$I$2:$I$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2132,7 +3614,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet2!$G$1</c15:sqref>
+                          <c15:sqref>'cdata epsilon'!$G$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2173,7 +3655,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet2!$B$2:$B$5</c15:sqref>
+                          <c15:sqref>'cdata epsilon'!$B$2:$B$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2200,7 +3682,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet2!$G$2:$G$5</c15:sqref>
+                          <c15:sqref>'cdata epsilon'!$G$2:$G$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2236,10 +3718,10 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet2!$K$1</c15:sqref>
+                          <c15:sqref>'cdata epsilon'!$K$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2277,10 +3759,10 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet2!$B$2:$B$5</c15:sqref>
+                          <c15:sqref>'cdata epsilon'!$B$2:$B$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2304,10 +3786,10 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet2!$K$2:$K$5</c15:sqref>
+                          <c15:sqref>'cdata epsilon'!$K$2:$K$5</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2330,7 +3812,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-55AA-4A41-BCB6-F3D862E6A054}"/>
                   </c:ext>
@@ -2707,6 +4189,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -4256,6 +5858,1554 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4776,15 +7926,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>510540</xdr:colOff>
+      <xdr:colOff>343829</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>697230</xdr:rowOff>
+      <xdr:rowOff>93205</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1146810</xdr:rowOff>
+      <xdr:colOff>576146</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>92927</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4811,16 +7961,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1432560</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>50737</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>244953</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>1005840</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>250902</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>102218</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4849,16 +7999,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>426720</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>1181100</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>166525</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>182694</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>475043</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>144779</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4889,6 +8039,119 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>689610</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC9C95A2-D2E3-4DB6-BD60-B2F9E671B45F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>87630</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>506730</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E11DD4D-E4B5-4A3E-830D-13563F66AEC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFB57D66-DB4C-4F41-B0FE-68444616A2CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5192,429 +8455,1274 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CE66C11-497F-4BAD-A297-C140DE8F8B95}">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="4" customWidth="1"/>
+    <col min="5" max="8" width="8.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" customWidth="1"/>
     <col min="12" max="17" width="0" hidden="1" customWidth="1"/>
     <col min="19" max="23" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="3">
+        <v>23.976868146043799</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.70924004384359796</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.55353798523042896</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8.2672139664071604</v>
+      </c>
+      <c r="F2" s="2">
+        <v>4.9284034311393201</v>
+      </c>
+      <c r="G2" s="2">
+        <v>5.7363358065724803</v>
+      </c>
+      <c r="H2" s="2">
+        <v>10.682204212591399</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6.4610741300721699</v>
+      </c>
+      <c r="J2" s="2">
+        <v>7.6978096438446304</v>
+      </c>
+      <c r="K2" s="2">
+        <v>4963.8773679733204</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1394.84722948074</v>
+      </c>
+      <c r="M2" s="2">
+        <v>1845.10709166526</v>
+      </c>
+      <c r="N2" s="2">
+        <v>25</v>
+      </c>
+      <c r="O2" s="2">
+        <v>5474</v>
+      </c>
+      <c r="P2" s="2">
+        <v>136.73052815198801</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>8203.8316891193299</v>
+      </c>
+      <c r="R2" s="2">
+        <v>19207</v>
+      </c>
+      <c r="S2" s="2">
+        <v>2727</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0.44013838501903801</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0.74653375299372504</v>
+      </c>
+      <c r="V2" s="2">
+        <v>132461</v>
+      </c>
+      <c r="W2" s="2">
+        <v>414939</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.70924004384359796</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.55353798523042896</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.44013838501903801</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.74653375299372504</v>
-      </c>
-      <c r="F2" s="2">
-        <v>23.976868146043799</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="B3" s="3">
+        <v>14.9978621331353</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.73337230544388898</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.55983800164434405</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8.5147397498501007</v>
+      </c>
+      <c r="F3" s="2">
+        <v>4.24443066860026</v>
+      </c>
+      <c r="G3" s="2">
+        <v>5.27776901571651</v>
+      </c>
+      <c r="H3" s="2">
+        <v>10.9943399425701</v>
+      </c>
+      <c r="I3" s="2">
+        <v>5.9242952205638799</v>
+      </c>
+      <c r="J3" s="2">
+        <v>7.4735581566905296</v>
+      </c>
+      <c r="K3" s="2">
+        <v>6583.5351414680399</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1269.01271510124</v>
+      </c>
+      <c r="M3" s="2">
+        <v>1498.7497563362101</v>
+      </c>
+      <c r="N3" s="2">
+        <v>15</v>
+      </c>
+      <c r="O3" s="2">
+        <v>5474</v>
+      </c>
+      <c r="P3" s="2">
+        <v>155.85496021509101</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>9351.2976129055005</v>
+      </c>
+      <c r="R3" s="2">
+        <v>19207</v>
+      </c>
+      <c r="S3" s="2">
+        <v>2727</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0.46596531771812699</v>
+      </c>
+      <c r="U3" s="2">
+        <v>0.70379783362013204</v>
+      </c>
+      <c r="V3" s="2">
         <v>132461</v>
       </c>
-      <c r="H2" s="2">
+      <c r="W3" s="2">
         <v>414939</v>
       </c>
-      <c r="I2" s="2">
-        <v>8.2672139664071604</v>
-      </c>
-      <c r="J2" s="2">
-        <v>4.9284034311393201</v>
-      </c>
-      <c r="K2" s="2">
-        <v>5.7363358065724803</v>
-      </c>
-      <c r="L2" s="2">
-        <v>10.682204212591399</v>
-      </c>
-      <c r="M2" s="2">
-        <v>6.4610741300721699</v>
-      </c>
-      <c r="N2" s="2">
-        <v>7.6978096438446304</v>
-      </c>
-      <c r="O2" s="2">
-        <v>4963.8773679733204</v>
-      </c>
-      <c r="P2" s="2">
-        <v>1394.84722948074</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>1845.10709166526</v>
-      </c>
-      <c r="R2" s="2">
+    </row>
+    <row r="4" spans="1:23" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3">
+        <v>7.3646261980491197</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.72259408111067802</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.54226424862108402</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8.7051407717552696</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4.3567055869653597</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5.40894905246126</v>
+      </c>
+      <c r="H4" s="2">
+        <v>11.203591800959</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.0297271615041899</v>
+      </c>
+      <c r="J4" s="2">
+        <v>7.6114010142308297</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5059.42527604103</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1422.63944673538</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1966.33158445358</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="O4" s="2">
+        <v>5474</v>
+      </c>
+      <c r="P4" s="2">
+        <v>140.806605120499</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>8448.3963072299903</v>
+      </c>
+      <c r="R4" s="2">
+        <v>19207</v>
+      </c>
+      <c r="S4" s="2">
+        <v>2727</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0.45118419132707899</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0.68181311317981697</v>
+      </c>
+      <c r="V4" s="2">
+        <v>132461</v>
+      </c>
+      <c r="W4" s="2">
+        <v>414939</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="2">
+      <c r="B5" s="3">
+        <v>1.9904279458387499</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.72177201315306005</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.54272390851380203</v>
+      </c>
+      <c r="E5" s="2">
+        <v>8.8102144397220403</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4.2813004793063696</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5.3772165774258802</v>
+      </c>
+      <c r="H5" s="2">
+        <v>11.359580368952599</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5.7524061854957198</v>
+      </c>
+      <c r="J5" s="2">
+        <v>7.5038878153282198</v>
+      </c>
+      <c r="K5" s="2">
+        <v>6572.8929276466297</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1253.7568855285599</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1516.5282146930599</v>
+      </c>
+      <c r="N5" s="2">
+        <v>2</v>
+      </c>
+      <c r="O5" s="2">
         <v>5474</v>
       </c>
-      <c r="T2" s="2">
-        <v>136.73052815198801</v>
-      </c>
-      <c r="U2" s="2">
-        <v>8203.8316891193299</v>
-      </c>
-      <c r="V2" s="2">
+      <c r="P5" s="2">
+        <v>155.71963379780399</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>9343.1780278682709</v>
+      </c>
+      <c r="R5" s="2">
         <v>19207</v>
       </c>
-      <c r="W2" s="2">
+      <c r="S5" s="2">
         <v>2727</v>
       </c>
+      <c r="T5" s="2">
+        <v>0.45036103852346498</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0.68510746898529196</v>
+      </c>
+      <c r="V5" s="2">
+        <v>132461</v>
+      </c>
+      <c r="W5" s="2">
+        <v>414939</v>
+      </c>
     </row>
-    <row r="3" spans="1:23" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.73337230544388898</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.55983800164434405</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.46596531771812699</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.70379783362013204</v>
-      </c>
-      <c r="F3" s="2">
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:23" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1.99</v>
+      </c>
+      <c r="B10">
+        <v>8.5336999999999996</v>
+      </c>
+      <c r="C10">
+        <v>8.2574000000000005</v>
+      </c>
+      <c r="D10">
+        <v>5.2592999999999996</v>
+      </c>
+      <c r="E10">
+        <v>4.8006000000000002</v>
+      </c>
+      <c r="F10">
+        <v>5.8423999999999996</v>
+      </c>
+      <c r="G10">
+        <v>6.1235999999999997</v>
+      </c>
+      <c r="H10">
+        <v>5.5610999999999997</v>
+      </c>
+      <c r="I10">
+        <v>0.43049999999999999</v>
+      </c>
+      <c r="L10">
+        <v>0.72540000000000004</v>
+      </c>
+      <c r="M10">
+        <v>0.53890000000000005</v>
+      </c>
+      <c r="N10">
+        <v>0.7016</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>14.510999999999999</v>
+      </c>
+      <c r="B11">
+        <v>8.5395000000000003</v>
+      </c>
+      <c r="C11">
+        <v>8.4219000000000008</v>
+      </c>
+      <c r="D11">
+        <v>5.1044</v>
+      </c>
+      <c r="E11">
+        <v>4.4683000000000002</v>
+      </c>
+      <c r="F11">
+        <v>5.6745999999999999</v>
+      </c>
+      <c r="G11">
+        <v>6.0110999999999999</v>
+      </c>
+      <c r="H11">
+        <v>5.3380999999999998</v>
+      </c>
+      <c r="I11">
+        <v>0.44130000000000003</v>
+      </c>
+      <c r="L11">
+        <v>0.70269999999999999</v>
+      </c>
+      <c r="M11">
+        <v>0.54210000000000003</v>
+      </c>
+      <c r="N11">
+        <v>0.7127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>24.995999999999999</v>
+      </c>
+      <c r="B12">
+        <v>8.2964000000000002</v>
+      </c>
+      <c r="C12">
+        <v>8.5945</v>
+      </c>
+      <c r="D12">
+        <v>5.5506000000000002</v>
+      </c>
+      <c r="E12">
+        <v>4.2797000000000001</v>
+      </c>
+      <c r="F12">
+        <v>5.7522000000000002</v>
+      </c>
+      <c r="G12">
+        <v>6.2754000000000003</v>
+      </c>
+      <c r="H12">
+        <v>5.2289000000000003</v>
+      </c>
+      <c r="I12">
+        <v>0.44180000000000003</v>
+      </c>
+      <c r="L12">
+        <v>0.70420000000000005</v>
+      </c>
+      <c r="M12">
+        <v>0.54269999999999996</v>
+      </c>
+      <c r="N12">
+        <v>0.71319999999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:23" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
         <v>14.9978621331353</v>
       </c>
-      <c r="G3" s="2">
-        <v>132461</v>
-      </c>
-      <c r="H3" s="2">
-        <v>414939</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="D16" s="2">
+        <v>5.27776901571651</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2">
         <v>8.5147397498501007</v>
       </c>
-      <c r="J3" s="2">
+      <c r="H16" s="2">
+        <v>8.5147397498501007</v>
+      </c>
+      <c r="I16" s="2">
         <v>4.24443066860026</v>
       </c>
-      <c r="K3" s="2">
-        <v>5.27776901571651</v>
-      </c>
-      <c r="L3" s="2">
-        <v>10.9943399425701</v>
-      </c>
-      <c r="M3" s="2">
-        <v>5.9242952205638799</v>
-      </c>
-      <c r="N3" s="2">
-        <v>7.4735581566905296</v>
-      </c>
-      <c r="O3" s="2">
-        <v>6583.5351414680399</v>
-      </c>
-      <c r="P3" s="2">
-        <v>1269.01271510124</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>1498.7497563362101</v>
-      </c>
-      <c r="R3" s="2">
-        <v>15</v>
-      </c>
-      <c r="S3" s="2">
-        <v>5474</v>
-      </c>
-      <c r="T3" s="2">
-        <v>155.85496021509101</v>
-      </c>
-      <c r="U3" s="2">
-        <v>9351.2976129055005</v>
-      </c>
-      <c r="V3" s="2">
-        <v>19207</v>
-      </c>
-      <c r="W3" s="2">
-        <v>2727</v>
+      <c r="J16" s="2">
+        <v>4.24443066860026</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.72259408111067802</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.54226424862108402</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.45118419132707899</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.68181311317981697</v>
-      </c>
-      <c r="F4" s="2">
-        <v>7.3646261980491197</v>
-      </c>
-      <c r="G4" s="2">
-        <v>132461</v>
-      </c>
-      <c r="H4" s="2">
-        <v>414939</v>
-      </c>
-      <c r="I4" s="2">
-        <v>8.7051407717552696</v>
-      </c>
-      <c r="J4" s="2">
-        <v>4.3567055869653597</v>
-      </c>
-      <c r="K4" s="2">
-        <v>5.40894905246126</v>
-      </c>
-      <c r="L4" s="2">
-        <v>11.203591800959</v>
-      </c>
-      <c r="M4" s="2">
-        <v>6.0297271615041899</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.6114010142308297</v>
-      </c>
-      <c r="O4" s="2">
-        <v>5059.42527604103</v>
-      </c>
-      <c r="P4" s="2">
-        <v>1422.63944673538</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>1966.33158445358</v>
-      </c>
-      <c r="R4" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="S4" s="2">
-        <v>5474</v>
-      </c>
-      <c r="T4" s="2">
-        <v>140.806605120499</v>
-      </c>
-      <c r="U4" s="2">
-        <v>8448.3963072299903</v>
-      </c>
-      <c r="V4" s="2">
-        <v>19207</v>
-      </c>
-      <c r="W4" s="2">
-        <v>2727</v>
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="2">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2">
+        <v>14.510999999999999</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5.8483000000000001</v>
+      </c>
+      <c r="E17" s="2">
+        <v>6.1131000000000002</v>
+      </c>
+      <c r="F17" s="2">
+        <v>5.5835999999999997</v>
+      </c>
+      <c r="G17" s="2">
+        <v>8.9765999999999995</v>
+      </c>
+      <c r="H17" s="2">
+        <v>8.5744000000000007</v>
+      </c>
+      <c r="I17" s="2">
+        <v>5.2497999999999996</v>
+      </c>
+      <c r="J17" s="2">
+        <v>4.8723999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="124.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.72177201315306005</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.54272390851380203</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.45036103852346498</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.68510746898529196</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1.9904279458387499</v>
-      </c>
-      <c r="G5" s="2">
-        <v>132461</v>
-      </c>
-      <c r="H5" s="2">
-        <v>414939</v>
-      </c>
-      <c r="I5" s="2">
-        <v>8.8102144397220403</v>
-      </c>
-      <c r="J5" s="2">
-        <v>4.2813004793063696</v>
-      </c>
-      <c r="K5" s="2">
-        <v>5.3772165774258802</v>
-      </c>
-      <c r="L5" s="2">
-        <v>11.359580368952599</v>
-      </c>
-      <c r="M5" s="2">
-        <v>5.7524061854957198</v>
-      </c>
-      <c r="N5" s="2">
-        <v>7.5038878153282198</v>
-      </c>
-      <c r="O5" s="2">
-        <v>6572.8929276466297</v>
-      </c>
-      <c r="P5" s="2">
-        <v>1253.7568855285599</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>1516.5282146930599</v>
-      </c>
-      <c r="R5" s="2">
-        <v>2</v>
-      </c>
-      <c r="S5" s="2">
-        <v>5474</v>
-      </c>
-      <c r="T5" s="2">
-        <v>155.71963379780399</v>
-      </c>
-      <c r="U5" s="2">
-        <v>9343.1780278682709</v>
-      </c>
-      <c r="V5" s="2">
-        <v>19207</v>
-      </c>
-      <c r="W5" s="2">
-        <v>2727</v>
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="2">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2">
+        <v>14.997999999999999</v>
+      </c>
+      <c r="D18" s="2">
+        <v>5.5797999999999996</v>
+      </c>
+      <c r="E18" s="2">
+        <v>6.2003000000000004</v>
+      </c>
+      <c r="F18" s="2">
+        <v>4.9592999999999998</v>
+      </c>
+      <c r="G18" s="2">
+        <v>9.8507999999999996</v>
+      </c>
+      <c r="H18" s="2">
+        <v>10.892099999999999</v>
+      </c>
+      <c r="I18" s="2">
+        <v>5.3421000000000003</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3.8397000000000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AEABCC-FE12-4367-8399-1B2C82131DA2}">
+  <dimension ref="A1:P49"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.99150000000000005</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3.7052999999999998</v>
+      </c>
+      <c r="E2" s="2">
+        <v>3.44</v>
+      </c>
+      <c r="F2" s="2">
+        <v>3.9706999999999999</v>
+      </c>
+      <c r="G2" s="2">
+        <v>10.796200000000001</v>
+      </c>
+      <c r="H2" s="2">
+        <v>9.8651999999999997</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2.1448999999999998</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2.3372999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="2">
+        <v>4.9960000000000004</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5.4405000000000001</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5.0808999999999997</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5.8002000000000002</v>
+      </c>
+      <c r="G3" s="2">
+        <v>8.5639000000000003</v>
+      </c>
+      <c r="H3" s="2">
+        <v>7.3129999999999997</v>
+      </c>
+      <c r="I3" s="2">
+        <v>4.4676</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5.3810000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="2">
+        <v>9.5340000000000007</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5.0491000000000001</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4.3883999999999999</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5.7098000000000004</v>
+      </c>
+      <c r="G4" s="2">
+        <v>9.3282000000000007</v>
+      </c>
+      <c r="H4" s="2">
+        <v>7.4292999999999996</v>
+      </c>
+      <c r="I4" s="2">
+        <v>3.5186999999999999</v>
+      </c>
+      <c r="J4" s="2">
+        <v>5.2333999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="2">
+        <v>14.994199999999999</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4.931</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4.6398999999999999</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5.2220000000000004</v>
+      </c>
+      <c r="G5" s="2">
+        <v>8.8496000000000006</v>
+      </c>
+      <c r="H5" s="2">
+        <v>7.8728999999999996</v>
+      </c>
+      <c r="I5" s="2">
+        <v>3.8988</v>
+      </c>
+      <c r="J5" s="2">
+        <v>4.4874000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="55.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="2">
+        <v>17.3291</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5.19</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4.6723999999999997</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5.7076000000000002</v>
+      </c>
+      <c r="G6" s="2">
+        <v>8.9639000000000006</v>
+      </c>
+      <c r="H6" s="2">
+        <v>7.4370000000000003</v>
+      </c>
+      <c r="I6" s="2">
+        <v>3.9167999999999998</v>
+      </c>
+      <c r="J6" s="2">
+        <v>5.2282999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="2">
+        <v>23.6371</v>
+      </c>
+      <c r="D7" s="2">
+        <v>5.2175000000000002</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4.9189999999999996</v>
+      </c>
+      <c r="F7" s="2">
+        <v>5.516</v>
+      </c>
+      <c r="G7" s="2">
+        <v>8.7787000000000006</v>
+      </c>
+      <c r="H7" s="2">
+        <v>7.5814000000000004</v>
+      </c>
+      <c r="I7" s="2">
+        <v>4.2393999999999998</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4.9436999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="2">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2">
+        <v>6.0740999999999996</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6.2510000000000003</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5.8971999999999998</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7.6802999999999999</v>
+      </c>
+      <c r="H8" s="2">
+        <v>7.165</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5.9993999999999996</v>
+      </c>
+      <c r="J8" s="2">
+        <v>5.5458999999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:16" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="C45" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.99150000000000005</v>
+      </c>
+      <c r="F45" s="2">
+        <v>3.7052999999999998</v>
+      </c>
+      <c r="G45" s="2">
+        <v>3.44</v>
+      </c>
+      <c r="H45" s="2">
+        <v>3.9706999999999999</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0.35549999999999998</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0.2356</v>
+      </c>
+      <c r="K45" s="2">
+        <v>0.28289999999999998</v>
+      </c>
+      <c r="L45" s="2">
+        <v>0.78269999999999995</v>
+      </c>
+      <c r="M45" s="2">
+        <v>10.796200000000001</v>
+      </c>
+      <c r="N45" s="2">
+        <v>9.8651999999999997</v>
+      </c>
+      <c r="O45" s="2">
+        <v>2.1448999999999998</v>
+      </c>
+      <c r="P45" s="2">
+        <v>2.3372999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="2">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="C46" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>15</v>
+      </c>
+      <c r="E46" s="2">
+        <v>14.994</v>
+      </c>
+      <c r="F46" s="2">
+        <v>4.931</v>
+      </c>
+      <c r="G46" s="2">
+        <v>4.6398999999999999</v>
+      </c>
+      <c r="H46" s="2">
+        <v>5.2220000000000004</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0.2782</v>
+      </c>
+      <c r="J46" s="2">
+        <v>0.58360000000000001</v>
+      </c>
+      <c r="K46" s="2">
+        <v>0.37640000000000001</v>
+      </c>
+      <c r="L46" s="2">
+        <v>0.64970000000000006</v>
+      </c>
+      <c r="M46" s="2">
+        <v>8.8496000000000006</v>
+      </c>
+      <c r="N46" s="2">
+        <v>7.8728999999999996</v>
+      </c>
+      <c r="O46" s="2">
+        <v>3.8988</v>
+      </c>
+      <c r="P46" s="2">
+        <v>4.4874000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="2">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="C47" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2">
+        <v>18</v>
+      </c>
+      <c r="E47" s="2">
+        <v>17.329000000000001</v>
+      </c>
+      <c r="F47" s="2">
+        <v>5.19</v>
+      </c>
+      <c r="G47" s="2">
+        <v>4.6723999999999997</v>
+      </c>
+      <c r="H47" s="2">
+        <v>5.7076000000000002</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0.2777</v>
+      </c>
+      <c r="J47" s="2">
+        <v>0.59060000000000001</v>
+      </c>
+      <c r="K47" s="2">
+        <v>0.3765</v>
+      </c>
+      <c r="L47" s="2">
+        <v>0.64459999999999995</v>
+      </c>
+      <c r="M47" s="2">
+        <v>8.9639000000000006</v>
+      </c>
+      <c r="N47" s="2">
+        <v>7.4370000000000003</v>
+      </c>
+      <c r="O47" s="2">
+        <v>3.9167999999999998</v>
+      </c>
+      <c r="P47" s="2">
+        <v>5.2282999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.312</v>
+      </c>
+      <c r="C48" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2">
+        <v>25</v>
+      </c>
+      <c r="E48" s="2">
+        <v>23.637</v>
+      </c>
+      <c r="F48" s="2">
+        <v>5.2175000000000002</v>
+      </c>
+      <c r="G48" s="2">
+        <v>4.9189999999999996</v>
+      </c>
+      <c r="H48" s="2">
+        <v>5.516</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0.27310000000000001</v>
+      </c>
+      <c r="J48" s="2">
+        <v>0.60509999999999997</v>
+      </c>
+      <c r="K48" s="2">
+        <v>0.37630000000000002</v>
+      </c>
+      <c r="L48" s="2">
+        <v>0.63639999999999997</v>
+      </c>
+      <c r="M48" s="2">
+        <v>8.7787000000000006</v>
+      </c>
+      <c r="N48" s="2">
+        <v>7.5814000000000004</v>
+      </c>
+      <c r="O48" s="2">
+        <v>4.2393999999999998</v>
+      </c>
+      <c r="P48" s="2">
+        <v>4.9436999999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0</v>
+      </c>
+      <c r="C49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2">
+        <v>18</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2">
+        <v>6.0740999999999996</v>
+      </c>
+      <c r="G49" s="2">
+        <v>6.2510000000000003</v>
+      </c>
+      <c r="H49" s="2">
+        <v>5.8971999999999998</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0.2797</v>
+      </c>
+      <c r="J49" s="2">
+        <v>0.60840000000000005</v>
+      </c>
+      <c r="K49" s="2">
+        <v>0.3821</v>
+      </c>
+      <c r="L49" s="2">
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="M49" s="2">
+        <v>7.6802999999999999</v>
+      </c>
+      <c r="N49" s="2">
+        <v>7.165</v>
+      </c>
+      <c r="O49" s="2">
+        <v>5.9993999999999996</v>
+      </c>
+      <c r="P49" s="2">
+        <v>5.5458999999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28251864-1456-4BBD-958C-1261E9ACD490}">
   <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5811,7 +9919,7 @@
         <v>1647.1224110136</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P5" s="2">
         <v>163.2525912186</v>
@@ -5819,7 +9927,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/cnn results/cnn result - epsilon.xlsx
+++ b/cnn results/cnn result - epsilon.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\flight delay\stpn paper\STPN-main\cnn results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1454E7FB-1C95-4AAE-B9D5-8A55CB95BD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959F6043-D07D-4CA6-B581-63111B757F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7584" yWindow="0" windowWidth="12336" windowHeight="11448" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
-    <sheet name="udata " sheetId="8" r:id="rId2"/>
-    <sheet name="cdata epsilon" sheetId="7" r:id="rId3"/>
+    <sheet name="time remove" sheetId="10" r:id="rId2"/>
+    <sheet name="time seq len" sheetId="9" r:id="rId3"/>
+    <sheet name="udata " sheetId="8" r:id="rId4"/>
+    <sheet name="cdata epsilon" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="104">
   <si>
     <t>classification_precision</t>
   </si>
@@ -289,6 +291,57 @@
   <si>
     <t>threshold</t>
   </si>
+  <si>
+    <t>time remove</t>
+  </si>
+  <si>
+    <t>cnnopacus_cdata_sigma0_43_train_results_table_20260117_023046 normal</t>
+  </si>
+  <si>
+    <t>timee remov</t>
+  </si>
+  <si>
+    <t>Final_Eps</t>
+  </si>
+  <si>
+    <t>Overall_MAE</t>
+  </si>
+  <si>
+    <t>Arr_MAE</t>
+  </si>
+  <si>
+    <t>Dep_MAE</t>
+  </si>
+  <si>
+    <t>Arr_Del_MAE</t>
+  </si>
+  <si>
+    <t>Dep_Del_MAE</t>
+  </si>
+  <si>
+    <t>Arr_NonDel_MAE</t>
+  </si>
+  <si>
+    <t>Dep_NonDel_MAE</t>
+  </si>
+  <si>
+    <t>Class_Acc</t>
+  </si>
+  <si>
+    <t>Class_F1</t>
+  </si>
+  <si>
+    <t>normal cdata</t>
+  </si>
+  <si>
+    <t>cdata no time</t>
+  </si>
+  <si>
+    <t>if time include, delay mae good, non delay bad</t>
+  </si>
+  <si>
+    <t>Seq Len</t>
+  </si>
 </sst>
 </file>
 
@@ -338,7 +391,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -361,11 +414,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -379,6 +441,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8455,7 +8520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CE66C11-497F-4BAD-A297-C140DE8F8B95}">
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -9033,7 +9098,7 @@
         <v>4.24443066860026</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>83</v>
       </c>
@@ -9065,7 +9130,7 @@
         <v>4.8723999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>84</v>
       </c>
@@ -9095,6 +9160,176 @@
       </c>
       <c r="J18" s="2">
         <v>3.8397000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="3">
+        <v>7.3646261980491197</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.72259408111067802</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.54226424862108402</v>
+      </c>
+      <c r="E25" s="2">
+        <v>8.7051407717552696</v>
+      </c>
+      <c r="F25" s="2">
+        <v>4.3567055869653597</v>
+      </c>
+      <c r="G25" s="2">
+        <v>5.40894905246126</v>
+      </c>
+      <c r="H25" s="2">
+        <v>11.203591800959</v>
+      </c>
+      <c r="I25" s="2">
+        <v>6.0297271615041899</v>
+      </c>
+      <c r="J25" s="2">
+        <v>7.6114010142308297</v>
+      </c>
+      <c r="K25" s="2">
+        <v>5059.42527604103</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1422.63944673538</v>
+      </c>
+      <c r="M25" s="2">
+        <v>1966.33158445358</v>
+      </c>
+      <c r="N25" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="O25" s="2">
+        <v>5474</v>
+      </c>
+      <c r="P25" s="2">
+        <v>140.806605120499</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>8448.3963072299903</v>
+      </c>
+      <c r="R25" s="2">
+        <v>19207</v>
+      </c>
+      <c r="S25" s="2">
+        <v>2727</v>
+      </c>
+      <c r="T25" s="2">
+        <v>0.45118419132707899</v>
+      </c>
+      <c r="U25" s="2">
+        <v>0.68181311317981697</v>
+      </c>
+      <c r="V25" s="2">
+        <v>132461</v>
+      </c>
+      <c r="W25" s="2">
+        <v>414939</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26">
+        <v>7.5</v>
+      </c>
+      <c r="C26">
+        <v>0.7137</v>
+      </c>
+      <c r="D26">
+        <v>0.54390000000000005</v>
+      </c>
+      <c r="E26">
+        <v>4.77029465956387</v>
+      </c>
+      <c r="F26">
+        <v>5.2037000000000004</v>
+      </c>
+      <c r="G26">
+        <v>5.66289482818891</v>
       </c>
     </row>
   </sheetData>
@@ -9105,6 +9340,390 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABFDE7E-B98D-4DEB-8254-0F537CE2C12A}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>23.976900000000001</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5.6333000000000002</v>
+      </c>
+      <c r="C2" s="2">
+        <v>6.0507</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5.2159000000000004</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8.5611999999999995</v>
+      </c>
+      <c r="F2" s="2">
+        <v>8.5363000000000007</v>
+      </c>
+      <c r="G2" s="2">
+        <v>5.1504000000000003</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4.2793999999999999</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.71479999999999999</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.54039999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>1.9676</v>
+      </c>
+      <c r="B3" s="2">
+        <v>5.7225000000000001</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5.9486999999999997</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5.4962999999999997</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8.7637999999999998</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8.2978000000000005</v>
+      </c>
+      <c r="G3" s="2">
+        <v>4.9390999999999998</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4.7061000000000002</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.70850000000000002</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.53610000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:12" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1.99</v>
+      </c>
+      <c r="B8">
+        <v>5.8423999999999996</v>
+      </c>
+      <c r="C8">
+        <v>6.1235999999999997</v>
+      </c>
+      <c r="D8">
+        <v>5.5610999999999997</v>
+      </c>
+      <c r="E8">
+        <v>8.5336999999999996</v>
+      </c>
+      <c r="F8">
+        <v>8.2574000000000005</v>
+      </c>
+      <c r="G8">
+        <v>5.2592999999999996</v>
+      </c>
+      <c r="H8">
+        <v>4.8006000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>24.995999999999999</v>
+      </c>
+      <c r="B9">
+        <v>5.7522000000000002</v>
+      </c>
+      <c r="C9">
+        <v>6.2754000000000003</v>
+      </c>
+      <c r="D9">
+        <v>5.2289000000000003</v>
+      </c>
+      <c r="E9">
+        <v>8.2964000000000002</v>
+      </c>
+      <c r="F9">
+        <v>8.5945</v>
+      </c>
+      <c r="G9">
+        <v>5.5506000000000002</v>
+      </c>
+      <c r="H9">
+        <v>4.2797000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79FCFF4-555F-46BC-B8A3-8309F0EF1E3D}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>5.5339999999999998</v>
+      </c>
+      <c r="D2">
+        <v>5.702</v>
+      </c>
+      <c r="E2">
+        <v>5.367</v>
+      </c>
+      <c r="F2">
+        <v>7.7709999999999999</v>
+      </c>
+      <c r="G2">
+        <v>7.8609999999999998</v>
+      </c>
+      <c r="H2">
+        <v>4.9589999999999996</v>
+      </c>
+      <c r="I2">
+        <v>4.6619999999999999</v>
+      </c>
+      <c r="J2">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="K2">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>6.6689999999999996</v>
+      </c>
+      <c r="D3">
+        <v>7.0490000000000004</v>
+      </c>
+      <c r="E3">
+        <v>6.2889999999999997</v>
+      </c>
+      <c r="F3">
+        <v>7.7350000000000003</v>
+      </c>
+      <c r="G3">
+        <v>7.8159999999999998</v>
+      </c>
+      <c r="H3">
+        <v>6.8019999999999996</v>
+      </c>
+      <c r="I3">
+        <v>5.8579999999999997</v>
+      </c>
+      <c r="J3">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="K3">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>5.5270000000000001</v>
+      </c>
+      <c r="D4">
+        <v>5.7480000000000002</v>
+      </c>
+      <c r="E4">
+        <v>5.306</v>
+      </c>
+      <c r="F4">
+        <v>7.6840000000000002</v>
+      </c>
+      <c r="G4">
+        <v>7.6619999999999999</v>
+      </c>
+      <c r="H4">
+        <v>5.0529999999999999</v>
+      </c>
+      <c r="I4">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J4">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="K4">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>6.0620000000000003</v>
+      </c>
+      <c r="D5">
+        <v>6.1929999999999996</v>
+      </c>
+      <c r="E5">
+        <v>5.93</v>
+      </c>
+      <c r="F5">
+        <v>7.96</v>
+      </c>
+      <c r="G5">
+        <v>7.7510000000000003</v>
+      </c>
+      <c r="H5">
+        <v>5.5590000000000002</v>
+      </c>
+      <c r="I5">
+        <v>5.4160000000000004</v>
+      </c>
+      <c r="J5">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="K5">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="L5" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3AEABCC-FE12-4367-8399-1B2C82131DA2}">
   <dimension ref="A1:P49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9670,7 +10289,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28251864-1456-4BBD-958C-1261E9ACD490}">
   <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/cnn results/cnn result - epsilon.xlsx
+++ b/cnn results/cnn result - epsilon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\flight delay\stpn paper\STPN-main\cnn results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959F6043-D07D-4CA6-B581-63111B757F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29874CED-8F26-490E-8561-3FBBD587D734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="108">
   <si>
     <t>classification_precision</t>
   </si>
@@ -342,6 +342,18 @@
   <si>
     <t>Seq Len</t>
   </si>
+  <si>
+    <t>Time Excluded</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>time excluded</t>
+  </si>
 </sst>
 </file>
 
@@ -427,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -444,6 +456,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2209,6 +2224,903 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'time seq len'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Overall_MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'time seq len'!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'time seq len'!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.6689999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.0620000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5339999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.5270000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D3CC-400F-82DE-02FA2E81A403}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'time seq len'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Arr_MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'time seq len'!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'time seq len'!$D$2:$D$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7.0490000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.1929999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.702</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.7480000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D3CC-400F-82DE-02FA2E81A403}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'time seq len'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Dep_MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'time seq len'!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'time seq len'!$E$2:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.2889999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.93</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.367</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.306</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D3CC-400F-82DE-02FA2E81A403}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'time seq len'!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Arr_NonDel_MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'time seq len'!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'time seq len'!$H$2:$H$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.8019999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5590000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9589999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.0529999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-D3CC-400F-82DE-02FA2E81A403}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'time seq len'!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Dep_NonDel_MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'time seq len'!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'time seq len'!$I$2:$I$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.8579999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.4160000000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.6619999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.6399999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-D3CC-400F-82DE-02FA2E81A403}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="622478528"/>
+        <c:axId val="622499744"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$F$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Arr_Del_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>24</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$F$2:$F$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>7.7350000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.96</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>7.7709999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>7.6840000000000002</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-D3CC-400F-82DE-02FA2E81A403}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$G$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Dep_Del_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>24</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$G$2:$G$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>7.8159999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.7510000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>7.8609999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>7.6619999999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-D3CC-400F-82DE-02FA2E81A403}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="622478528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="622499744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="622499744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="622478528"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
@@ -2550,7 +3462,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3166,7 +4078,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3521,7 +4433,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4374,6 +5286,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -7471,6 +8423,522 @@
 </file>
 
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8107,6 +9575,47 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37124248-348C-484B-A2BD-4E5EAFD1DB75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -8216,7 +9725,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -9535,8 +11044,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79FCFF4-555F-46BC-B8A3-8309F0EF1E3D}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -9575,151 +11088,306 @@
     </row>
     <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>5.5339999999999998</v>
+        <v>6.6689999999999996</v>
       </c>
       <c r="D2">
-        <v>5.702</v>
+        <v>7.0490000000000004</v>
       </c>
       <c r="E2">
-        <v>5.367</v>
+        <v>6.2889999999999997</v>
       </c>
       <c r="F2">
-        <v>7.7709999999999999</v>
+        <v>7.7350000000000003</v>
       </c>
       <c r="G2">
-        <v>7.8609999999999998</v>
+        <v>7.8159999999999998</v>
       </c>
       <c r="H2">
-        <v>4.9589999999999996</v>
+        <v>6.8019999999999996</v>
       </c>
       <c r="I2">
-        <v>4.6619999999999999</v>
+        <v>5.8579999999999997</v>
       </c>
       <c r="J2">
-        <v>0.73699999999999999</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="K2">
-        <v>0.59199999999999997</v>
-      </c>
-      <c r="L2" s="1"/>
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>6.6689999999999996</v>
+        <v>6.0620000000000003</v>
       </c>
       <c r="D3">
-        <v>7.0490000000000004</v>
+        <v>6.1929999999999996</v>
       </c>
       <c r="E3">
-        <v>6.2889999999999997</v>
+        <v>5.93</v>
       </c>
       <c r="F3">
-        <v>7.7350000000000003</v>
+        <v>7.96</v>
       </c>
       <c r="G3">
-        <v>7.8159999999999998</v>
+        <v>7.7510000000000003</v>
       </c>
       <c r="H3">
-        <v>6.8019999999999996</v>
+        <v>5.5590000000000002</v>
       </c>
       <c r="I3">
-        <v>5.8579999999999997</v>
+        <v>5.4160000000000004</v>
       </c>
       <c r="J3">
-        <v>0.69499999999999995</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="K3">
-        <v>0.55400000000000005</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>5.5270000000000001</v>
+        <v>5.5339999999999998</v>
       </c>
       <c r="D4">
-        <v>5.7480000000000002</v>
+        <v>5.702</v>
       </c>
       <c r="E4">
-        <v>5.306</v>
+        <v>5.367</v>
       </c>
       <c r="F4">
-        <v>7.6840000000000002</v>
+        <v>7.7709999999999999</v>
       </c>
       <c r="G4">
-        <v>7.6619999999999999</v>
+        <v>7.8609999999999998</v>
       </c>
       <c r="H4">
-        <v>5.0529999999999999</v>
+        <v>4.9589999999999996</v>
       </c>
       <c r="I4">
-        <v>4.6399999999999997</v>
+        <v>4.6619999999999999</v>
       </c>
       <c r="J4">
         <v>0.73699999999999999</v>
       </c>
       <c r="K4">
-        <v>0.60199999999999998</v>
-      </c>
-      <c r="L4" s="2"/>
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>6.0620000000000003</v>
+        <v>5.5270000000000001</v>
       </c>
       <c r="D5">
-        <v>6.1929999999999996</v>
+        <v>5.7480000000000002</v>
       </c>
       <c r="E5">
-        <v>5.93</v>
+        <v>5.306</v>
       </c>
       <c r="F5">
-        <v>7.96</v>
+        <v>7.6840000000000002</v>
       </c>
       <c r="G5">
-        <v>7.7510000000000003</v>
+        <v>7.6619999999999999</v>
       </c>
       <c r="H5">
-        <v>5.5590000000000002</v>
+        <v>5.0529999999999999</v>
       </c>
       <c r="I5">
-        <v>5.4160000000000004</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="J5">
-        <v>0.70799999999999996</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="K5">
-        <v>0.57199999999999995</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="L5" s="2"/>
+    </row>
+    <row r="7" spans="1:12" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>5.6820000000000004</v>
+      </c>
+      <c r="E8">
+        <v>5.9960000000000004</v>
+      </c>
+      <c r="F8">
+        <v>5.3680000000000003</v>
+      </c>
+      <c r="G8">
+        <v>9.7789999999999999</v>
+      </c>
+      <c r="H8">
+        <v>10.167</v>
+      </c>
+      <c r="I8">
+        <v>4.6369999999999996</v>
+      </c>
+      <c r="J8">
+        <v>4.0119999999999996</v>
+      </c>
+      <c r="K8">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="L8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>6.944</v>
+      </c>
+      <c r="E9">
+        <v>7.133</v>
+      </c>
+      <c r="F9">
+        <v>6.7539999999999996</v>
+      </c>
+      <c r="G9">
+        <v>10.885</v>
+      </c>
+      <c r="H9">
+        <v>11.859</v>
+      </c>
+      <c r="I9">
+        <v>5.7850000000000001</v>
+      </c>
+      <c r="J9">
+        <v>5.3120000000000003</v>
+      </c>
+      <c r="K9">
+        <v>0.68</v>
+      </c>
+      <c r="L9">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>6.59</v>
+      </c>
+      <c r="E10">
+        <v>6.4950000000000001</v>
+      </c>
+      <c r="F10">
+        <v>6.6859999999999999</v>
+      </c>
+      <c r="G10">
+        <v>10.925000000000001</v>
+      </c>
+      <c r="H10">
+        <v>11.989000000000001</v>
+      </c>
+      <c r="I10">
+        <v>4.8959999999999999</v>
+      </c>
+      <c r="J10">
+        <v>5.181</v>
+      </c>
+      <c r="K10">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="L10">
+        <v>0.13700000000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/cnn results/cnn result - epsilon.xlsx
+++ b/cnn results/cnn result - epsilon.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\flight delay\stpn paper\STPN-main\cnn results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39874CCE-2EF3-40FB-8098-A28794A65A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC2A3EE-9B89-43F5-BCA4-4538660519C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="731" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="731" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
     <sheet name="horizons" sheetId="11" r:id="rId2"/>
     <sheet name="delay threshold" sheetId="12" r:id="rId3"/>
-    <sheet name="time remove" sheetId="10" r:id="rId4"/>
-    <sheet name="cnnn kant" sheetId="13" r:id="rId5"/>
+    <sheet name="cnnn kant" sheetId="13" r:id="rId4"/>
+    <sheet name="time remove" sheetId="10" r:id="rId5"/>
     <sheet name="negative keep" sheetId="14" r:id="rId6"/>
     <sheet name="time seq len" sheetId="9" r:id="rId7"/>
     <sheet name="udata " sheetId="8" r:id="rId8"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="204">
   <si>
     <t>classification_precision</t>
   </si>
@@ -532,9 +532,6 @@
     <t>21:51 Run cnnopacus_-_deepDualReg_-_Copy_cdata_sigma0_00_dualreg_train_results_table_20260125_215110.csv​</t>
   </si>
   <si>
-    <t>only cnn</t>
-  </si>
-  <si>
     <t>cnn+kan</t>
   </si>
   <si>
@@ -612,12 +609,48 @@
   <si>
     <t>kan only</t>
   </si>
+  <si>
+    <t>cnnopacus_-_deepDualReg_-_kan_-_time_enable_stage3_cdata_sigma0_00_dualreg_train_results_table_20260127_145240</t>
+  </si>
+  <si>
+    <t>only deeper cnn</t>
+  </si>
+  <si>
+    <t>cnnopacus_-_deepDualReg_-_not_flatten_cdata_sigma0_44_dualreg_train_results_table_eps7.19</t>
+  </si>
+  <si>
+    <t>delay good</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>eps 7.31 cnnopacus_-_deepDualReg_-_kan_-_time_enable_stage3_cdata_sigma0_44_dualreg_train_results_table_e.csv​</t>
+  </si>
+  <si>
+    <t>eps 7.50 cnnopacus_-_deepDualReg_-_kan_-_time_enable_stage3_cdata_sigma0_44_dualreg_train_results_table_e.csv​</t>
+  </si>
+  <si>
+    <t>deepDualReg-KAN-Time Sigma 0.44 (DualReg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">normal without negative val </t>
+  </si>
+  <si>
+    <t>cnnopacus_-_deepDualReg_-_not_flatten_cdata_sigma0_44_dualreg_noDP</t>
+  </si>
+  <si>
+    <t>cnnopacus_-_deepDualReg_-_kan_-_time_enable_stage3NotFlat_cdata_sigma0_00_dualreg_train_results_table_20260131_194434</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -645,6 +678,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -697,7 +736,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -719,6 +758,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1535,10 +1578,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'time seq len'!$A$14:$A$18</c:f>
+              <c:f>'time seq len'!$A$14:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -1551,18 +1594,15 @@
                 <c:pt idx="3">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>48</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'time seq len'!$G$14:$G$18</c:f>
+              <c:f>'time seq len'!$G$14:$G$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>8.5154999999999994</c:v>
                 </c:pt>
@@ -1574,9 +1614,6 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>7.9972000000000003</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.9379</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1650,13 +1687,13 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -1668,9 +1705,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1680,13 +1714,13 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$D$14:$D$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$D$14:$D$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>5.4481999999999999</c:v>
                       </c:pt>
@@ -1698,9 +1732,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>5.1707999999999998</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>5.1097999999999999</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1719,7 +1750,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$E$13</c15:sqref>
@@ -1760,16 +1791,16 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -1781,25 +1812,22 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$E$14:$E$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$E$14:$E$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>5.7355</c:v>
                       </c:pt>
@@ -1811,9 +1839,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>5.3566000000000003</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>5.2422000000000004</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1832,7 +1857,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$F$13</c15:sqref>
@@ -1873,16 +1898,16 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -1894,25 +1919,22 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$F$14:$F$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$F$14:$F$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>5.1608999999999998</c:v>
                       </c:pt>
@@ -1924,9 +1946,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>4.9850000000000003</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>4.9774000000000003</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1945,7 +1964,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$H$13</c15:sqref>
@@ -1986,16 +2005,16 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -2007,25 +2026,22 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$H$14:$H$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$H$14:$H$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8.4483999999999995</c:v>
                       </c:pt>
@@ -2037,9 +2053,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>7.8518999999999997</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>8.0442</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -2058,7 +2071,7 @@
                 <c:order val="5"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$I$13</c15:sqref>
@@ -2099,16 +2112,16 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -2120,25 +2133,22 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$I$14:$I$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$I$14:$I$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>4.7385000000000002</c:v>
                       </c:pt>
@@ -2150,9 +2160,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>4.4078999999999997</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>4.2690000000000001</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -2171,7 +2178,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$J$13</c15:sqref>
@@ -2218,16 +2225,16 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -2239,25 +2246,22 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$J$14:$J$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$J$14:$J$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>4.2336</c:v>
                       </c:pt>
@@ -2269,9 +2273,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>4.1749999999999998</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>4.1071999999999997</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -2556,7 +2557,6 @@
                   <c:v>Overall_MAE</c:v>
                 </c:pt>
               </c:strCache>
-              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -2585,10 +2585,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'time seq len'!$A$14:$A$18</c:f>
+              <c:f>'time seq len'!$A$14:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -2601,19 +2601,15 @@
                 <c:pt idx="3">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>48</c:v>
-                </c:pt>
               </c:numCache>
-              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'time seq len'!$D$14:$D$18</c:f>
+              <c:f>'time seq len'!$D$14:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>5.4481999999999999</c:v>
                 </c:pt>
@@ -2626,11 +2622,7 @@
                 <c:pt idx="3">
                   <c:v>5.1707999999999998</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.1097999999999999</c:v>
-                </c:pt>
               </c:numCache>
-              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
@@ -2702,13 +2694,13 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -2720,9 +2712,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -2732,13 +2721,13 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$E$14:$E$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$E$14:$E$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>5.7355</c:v>
                       </c:pt>
@@ -2750,9 +2739,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>5.3566000000000003</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>5.2422000000000004</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -2771,7 +2757,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$F$13</c15:sqref>
@@ -2812,16 +2798,16 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -2833,25 +2819,22 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$F$14:$F$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$F$14:$F$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>5.1608999999999998</c:v>
                       </c:pt>
@@ -2863,9 +2846,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>4.9850000000000003</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>4.9774000000000003</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -2884,7 +2864,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$G$13</c15:sqref>
@@ -2925,16 +2905,16 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -2946,25 +2926,22 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$G$14:$G$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$G$14:$G$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8.5154999999999994</c:v>
                       </c:pt>
@@ -2976,9 +2953,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>7.9972000000000003</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>7.9379</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -2997,7 +2971,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$H$13</c15:sqref>
@@ -3038,16 +3012,16 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -3059,25 +3033,22 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$H$14:$H$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$H$14:$H$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8.4483999999999995</c:v>
                       </c:pt>
@@ -3089,9 +3060,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>7.8518999999999997</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>8.0442</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -3110,7 +3078,7 @@
                 <c:order val="5"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$I$13</c15:sqref>
@@ -3151,16 +3119,16 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -3172,25 +3140,22 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$I$14:$I$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$I$14:$I$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>4.7385000000000002</c:v>
                       </c:pt>
@@ -3202,9 +3167,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>4.4078999999999997</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>4.2690000000000001</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -3223,7 +3185,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$J$13</c15:sqref>
@@ -3270,16 +3232,16 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$14:$A$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>8</c:v>
                       </c:pt>
@@ -3291,25 +3253,22 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>48</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$J$14:$J$18</c15:sqref>
+                          <c15:sqref>'time seq len'!$J$14:$J$17</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="5"/>
+                      <c:ptCount val="4"/>
                       <c:pt idx="0">
                         <c:v>4.2336</c:v>
                       </c:pt>
@@ -3321,9 +3280,6 @@
                       </c:pt>
                       <c:pt idx="3">
                         <c:v>4.1749999999999998</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>4.1071999999999997</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -9058,303 +9014,12 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'time remove'!$C$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Overall_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'time remove'!$B$16:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1.9770000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.1420000000000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>14.068</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23.295999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'time remove'!$C$16:$C$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.7869999999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.1989999999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.3769999999999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.2320000000000002</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-10FD-491C-BBA9-FC4699357C98}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'time remove'!$D$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Arr_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'time remove'!$B$16:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1.9770000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.1420000000000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>14.068</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23.295999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'time remove'!$D$16:$D$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>5.0030000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.5270000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.609</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.4080000000000004</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-10FD-491C-BBA9-FC4699357C98}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'time remove'!$E$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Dep_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'time remove'!$B$16:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1.9770000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.1420000000000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>14.068</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23.295999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'time remove'!$E$16:$E$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4.5709999999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.87</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.1440000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.0570000000000004</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-10FD-491C-BBA9-FC4699357C98}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
@@ -9443,197 +9108,15 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
+          <c:idx val="9"/>
+          <c:order val="9"/>
           <c:tx>
-            <c:strRef>
-              <c:f>'time remove'!$G$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Dep_Del_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>noDP</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'time remove'!$B$16:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1.9770000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.1420000000000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>14.068</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23.295999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'time remove'!$G$16:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>8.8789999999999996</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>8.359</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.093</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.1319999999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-10FD-491C-BBA9-FC4699357C98}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'time remove'!$H$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Arr_NonDel_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'time remove'!$B$16:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1.9770000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.1420000000000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>14.068</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23.295999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'time remove'!$H$16:$H$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>3.7050000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.6660000000000004</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.79</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.4770000000000003</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-10FD-491C-BBA9-FC4699357C98}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'time remove'!$I$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Dep_NonDel_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent4">
                   <a:lumMod val="60000"/>
                 </a:schemeClr>
               </a:solidFill>
@@ -9646,13 +9129,13 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent4">
                   <a:lumMod val="60000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent1">
+                  <a:schemeClr val="accent4">
                     <a:lumMod val="60000"/>
                   </a:schemeClr>
                 </a:solidFill>
@@ -9683,21 +9166,21 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'time remove'!$I$16:$I$19</c:f>
+              <c:f>('time remove'!$F$20,'time remove'!$F$20,'time remove'!$F$20,'time remove'!$F$20)</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3.379</c:v>
+                  <c:v>7.7709999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.9049999999999998</c:v>
+                  <c:v>7.7709999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.3289999999999997</c:v>
+                  <c:v>7.7709999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.2060000000000004</c:v>
+                  <c:v>7.7709999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9705,7 +9188,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-10FD-491C-BBA9-FC4699357C98}"/>
+              <c16:uniqueId val="{00000001-5DFF-42FB-B723-DECF180DDE73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9723,12 +9206,660 @@
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredScatterSeries>
               <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$C$15</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Overall_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>1.9770000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.1420000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.068</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>23.295999999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$C$16:$C$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>4.7869999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>5.1989999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5.3769999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5.2320000000000002</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-10FD-491C-BBA9-FC4699357C98}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$D$15</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Arr_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>1.9770000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.1420000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.068</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>23.295999999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$D$16:$D$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>5.0030000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>5.5270000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5.609</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5.4080000000000004</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-10FD-491C-BBA9-FC4699357C98}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$E$15</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Dep_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>1.9770000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.1420000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.068</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>23.295999999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$E$16:$E$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>4.5709999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>4.87</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5.1440000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5.0570000000000004</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-10FD-491C-BBA9-FC4699357C98}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$G$15</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Dep_Del_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>1.9770000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.1420000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.068</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>23.295999999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$G$16:$G$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>8.8789999999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8.359</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>8.093</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>8.1319999999999997</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-10FD-491C-BBA9-FC4699357C98}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="5"/>
+                <c:order val="5"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$H$15</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Arr_NonDel_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>1.9770000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.1420000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.068</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>23.295999999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$H$16:$H$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>3.7050000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>4.6660000000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>4.79</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4.4770000000000003</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000006-10FD-491C-BBA9-FC4699357C98}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="6"/>
+                <c:order val="6"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$I$15</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Dep_NonDel_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>1.9770000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.1420000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.068</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>23.295999999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time remove'!$I$16:$I$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>3.379</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>3.9049999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>4.3289999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4.2060000000000004</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000007-10FD-491C-BBA9-FC4699357C98}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
                 <c:idx val="7"/>
                 <c:order val="7"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$J$15</c15:sqref>
                         </c15:formulaRef>
@@ -9774,8 +9905,8 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
                         </c15:formulaRef>
@@ -9801,8 +9932,8 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$J$16:$J$19</c15:sqref>
                         </c15:formulaRef>
@@ -9827,7 +9958,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000008-10FD-491C-BBA9-FC4699357C98}"/>
                   </c:ext>
@@ -10266,180 +10397,6 @@
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'time seq len'!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Arr_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'time seq len'!$A$2:$A$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>24</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'time seq len'!$D$2:$D$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>7.0490000000000004</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.1929999999999996</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.702</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.7480000000000002</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D3CC-400F-82DE-02FA2E81A403}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'time seq len'!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Dep_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'time seq len'!$A$2:$A$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>24</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'time seq len'!$E$2:$E$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>6.2889999999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.93</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.367</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.306</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D3CC-400F-82DE-02FA2E81A403}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
           <c:idx val="5"/>
           <c:order val="5"/>
           <c:tx>
@@ -10633,12 +10590,226 @@
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredScatterSeries>
               <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Arr_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>24</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$D$2:$D$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>7.0490000000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>6.1929999999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5.702</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5.7480000000000002</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-D3CC-400F-82DE-02FA2E81A403}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$E$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Dep_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>24</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$E$2:$E$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>6.2889999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>5.93</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5.367</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5.306</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-D3CC-400F-82DE-02FA2E81A403}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
                 <c:idx val="3"/>
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$F$1</c15:sqref>
                         </c15:formulaRef>
@@ -10678,8 +10849,8 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
                         </c15:formulaRef>
@@ -10705,8 +10876,8 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$F$2:$F$5</c15:sqref>
                         </c15:formulaRef>
@@ -10731,7 +10902,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-D3CC-400F-82DE-02FA2E81A403}"/>
                   </c:ext>
@@ -19121,12 +19292,12 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>125730</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>30892</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>576649</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
@@ -19166,8 +19337,8 @@
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>129540</xdr:colOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>587828</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -20173,33 +20344,33 @@
     <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:23" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B17" s="2">
         <v>6.665</v>
@@ -21370,6 +21541,1031 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BEF8BD2-3303-4A9E-9D3E-030E648328A8}">
+  <dimension ref="A1:Q76"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="41.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5.89</v>
+      </c>
+      <c r="D2" s="2">
+        <v>6.07</v>
+      </c>
+      <c r="E2" s="2">
+        <v>5.72</v>
+      </c>
+      <c r="F2" s="2">
+        <v>7.43</v>
+      </c>
+      <c r="G2" s="3">
+        <v>7.56</v>
+      </c>
+      <c r="H2" s="2">
+        <v>5.59</v>
+      </c>
+      <c r="I2" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="L2" t="s">
+        <v>166</v>
+      </c>
+      <c r="M2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="2">
+        <v>11.51</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5.18</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5.59</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4.78</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8.32</v>
+      </c>
+      <c r="G3" s="3">
+        <v>8.64</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="I3" s="2">
+        <v>3.68</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.754</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.58399999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>5.5339999999999998</v>
+      </c>
+      <c r="D4">
+        <v>5.702</v>
+      </c>
+      <c r="E4">
+        <v>5.367</v>
+      </c>
+      <c r="F4">
+        <v>7.7709999999999999</v>
+      </c>
+      <c r="G4" s="4">
+        <v>7.8609999999999998</v>
+      </c>
+      <c r="H4">
+        <v>4.9589999999999996</v>
+      </c>
+      <c r="I4">
+        <v>4.6619999999999999</v>
+      </c>
+      <c r="J4">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="K4">
+        <v>0.59199999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="2">
+        <v>7.31</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="D9" s="2">
+        <v>5.09</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4.79</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8.58</v>
+      </c>
+      <c r="G9" s="2">
+        <v>8.57</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3.84</v>
+      </c>
+      <c r="I9" s="2">
+        <v>3.73</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="L9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>4.68</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="F10" s="2">
+        <v>9.15</v>
+      </c>
+      <c r="G10" s="2">
+        <v>8.89</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3.35</v>
+      </c>
+      <c r="I10" s="2">
+        <v>3.23</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0.55700000000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>5.5339999999999998</v>
+      </c>
+      <c r="D11">
+        <v>5.702</v>
+      </c>
+      <c r="E11">
+        <v>5.367</v>
+      </c>
+      <c r="F11">
+        <v>7.7709999999999999</v>
+      </c>
+      <c r="G11" s="4">
+        <v>7.8609999999999998</v>
+      </c>
+      <c r="H11">
+        <v>4.9589999999999996</v>
+      </c>
+      <c r="I11">
+        <v>4.6619999999999999</v>
+      </c>
+      <c r="J11">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="K11">
+        <v>0.59199999999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>5.32</v>
+      </c>
+      <c r="D15" s="2">
+        <v>5.38</v>
+      </c>
+      <c r="E15" s="2">
+        <v>5.26</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="G15" s="2">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="H15" s="2">
+        <v>4.22</v>
+      </c>
+      <c r="I15" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="L15" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q18" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:17" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1044.8499999999999</v>
+      </c>
+      <c r="C21" s="2">
+        <v>5.4298000000000002</v>
+      </c>
+      <c r="D21" s="2">
+        <v>5.7060000000000004</v>
+      </c>
+      <c r="E21" s="2">
+        <v>5.1535000000000002</v>
+      </c>
+      <c r="F21" s="2">
+        <v>8.8309999999999995</v>
+      </c>
+      <c r="G21" s="3">
+        <v>7.6388999999999996</v>
+      </c>
+      <c r="H21" s="2">
+        <v>2.3407</v>
+      </c>
+      <c r="I21" s="2">
+        <v>2.0931000000000002</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.43169999999999997</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0.84689999999999999</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0.57120000000000004</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0.69359999999999999</v>
+      </c>
+      <c r="N21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:17" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>5.83</v>
+      </c>
+      <c r="D24" s="2">
+        <v>5.92</v>
+      </c>
+      <c r="E24" s="2">
+        <v>5.75</v>
+      </c>
+      <c r="F24" s="2">
+        <v>7.67</v>
+      </c>
+      <c r="G24" s="2">
+        <v>7.66</v>
+      </c>
+      <c r="H24" s="2">
+        <v>5.29</v>
+      </c>
+      <c r="I24" s="2">
+        <v>5.21</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="L24" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="3">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3">
+        <v>5.2933000000000003</v>
+      </c>
+      <c r="D25" s="3">
+        <v>5.4629000000000003</v>
+      </c>
+      <c r="E25" s="3">
+        <v>5.1237000000000004</v>
+      </c>
+      <c r="F25" s="3">
+        <v>8.1595999999999993</v>
+      </c>
+      <c r="G25" s="3">
+        <v>7.9936999999999996</v>
+      </c>
+      <c r="H25" s="3">
+        <v>4.4946999999999999</v>
+      </c>
+      <c r="I25" s="3">
+        <v>4.3133999999999997</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.72960000000000003</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.57879999999999998</v>
+      </c>
+      <c r="L25" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="55.8" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="2">
+        <v>7.31</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="D26" s="2">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="E26" s="2">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="F26" s="2">
+        <v>8.91</v>
+      </c>
+      <c r="G26" s="2">
+        <v>8.66</v>
+      </c>
+      <c r="H26" s="2">
+        <v>3.45</v>
+      </c>
+      <c r="I26" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0.77</v>
+      </c>
+      <c r="K26" s="2">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B27" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="C27" s="2">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4.84</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4.43</v>
+      </c>
+      <c r="F27" s="2">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="G27" s="2">
+        <v>9.11</v>
+      </c>
+      <c r="H27" s="2">
+        <v>3.33</v>
+      </c>
+      <c r="I27" s="2">
+        <v>3.11</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="M27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+    </row>
+    <row r="30" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:17" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="2">
+        <v>7.19</v>
+      </c>
+      <c r="C32" s="2">
+        <v>5.46</v>
+      </c>
+      <c r="D32" s="2">
+        <v>5.44</v>
+      </c>
+      <c r="E32" s="2">
+        <v>5.47</v>
+      </c>
+      <c r="F32" s="2">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="G32" s="2">
+        <v>7.88</v>
+      </c>
+      <c r="H32" s="2">
+        <v>4.51</v>
+      </c>
+      <c r="I32" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0.73199999999999998</v>
+      </c>
+      <c r="K32" s="2">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="L32" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>5.79</v>
+      </c>
+      <c r="D33" s="2">
+        <v>6.13</v>
+      </c>
+      <c r="E33" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="F33" s="2">
+        <v>7.53</v>
+      </c>
+      <c r="G33" s="2">
+        <v>7.78</v>
+      </c>
+      <c r="H33" s="2">
+        <v>5.63</v>
+      </c>
+      <c r="I33" s="2">
+        <v>4.79</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="L33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>125</v>
+      </c>
+      <c r="B53">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>138</v>
+      </c>
+      <c r="B65" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>140</v>
+      </c>
+      <c r="B66">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" s="8">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68">
+        <v>0.38082122802734297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>143</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70">
+        <v>1.3335416992238299E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>145</v>
+      </c>
+      <c r="B71">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>146</v>
+      </c>
+      <c r="B72" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>148</v>
+      </c>
+      <c r="B73" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABFDE7E-B98D-4DEB-8254-0F537CE2C12A}">
   <dimension ref="A1:L60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -21998,658 +23194,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BEF8BD2-3303-4A9E-9D3E-030E648328A8}">
-  <dimension ref="A1:N73"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="41.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>5.89</v>
-      </c>
-      <c r="D2" s="2">
-        <v>6.07</v>
-      </c>
-      <c r="E2" s="2">
-        <v>5.72</v>
-      </c>
-      <c r="F2" s="2">
-        <v>7.43</v>
-      </c>
-      <c r="G2" s="3">
-        <v>7.56</v>
-      </c>
-      <c r="H2" s="2">
-        <v>5.59</v>
-      </c>
-      <c r="I2" s="2">
-        <v>5.2</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.72899999999999998</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.59099999999999997</v>
-      </c>
-      <c r="L2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="2">
-        <v>11.51</v>
-      </c>
-      <c r="C3" s="2">
-        <v>5.18</v>
-      </c>
-      <c r="D3" s="2">
-        <v>5.59</v>
-      </c>
-      <c r="E3" s="2">
-        <v>4.78</v>
-      </c>
-      <c r="F3" s="2">
-        <v>8.32</v>
-      </c>
-      <c r="G3" s="3">
-        <v>8.64</v>
-      </c>
-      <c r="H3" s="2">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="I3" s="2">
-        <v>3.68</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.754</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0.58399999999999996</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>5.5339999999999998</v>
-      </c>
-      <c r="D4">
-        <v>5.702</v>
-      </c>
-      <c r="E4">
-        <v>5.367</v>
-      </c>
-      <c r="F4">
-        <v>7.7709999999999999</v>
-      </c>
-      <c r="G4" s="4">
-        <v>7.8609999999999998</v>
-      </c>
-      <c r="H4">
-        <v>4.9589999999999996</v>
-      </c>
-      <c r="I4">
-        <v>4.6619999999999999</v>
-      </c>
-      <c r="J4">
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="K4">
-        <v>0.59199999999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="2">
-        <v>7.31</v>
-      </c>
-      <c r="C9" s="2">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="D9" s="2">
-        <v>5.09</v>
-      </c>
-      <c r="E9" s="2">
-        <v>4.79</v>
-      </c>
-      <c r="F9" s="2">
-        <v>8.58</v>
-      </c>
-      <c r="G9" s="2">
-        <v>8.57</v>
-      </c>
-      <c r="H9" s="2">
-        <v>3.84</v>
-      </c>
-      <c r="I9" s="2">
-        <v>3.73</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0.76500000000000001</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0.55800000000000005</v>
-      </c>
-      <c r="L9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B10" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>4.68</v>
-      </c>
-      <c r="D10" s="2">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="E10" s="2">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="F10" s="2">
-        <v>9.15</v>
-      </c>
-      <c r="G10" s="2">
-        <v>8.89</v>
-      </c>
-      <c r="H10" s="2">
-        <v>3.35</v>
-      </c>
-      <c r="I10" s="2">
-        <v>3.23</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0.76700000000000002</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0.55700000000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>5.32</v>
-      </c>
-      <c r="D15" s="2">
-        <v>5.38</v>
-      </c>
-      <c r="E15" s="2">
-        <v>5.26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>8.6199999999999992</v>
-      </c>
-      <c r="G15" s="2">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="H15" s="2">
-        <v>4.22</v>
-      </c>
-      <c r="I15" s="2">
-        <v>4.38</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0.74299999999999999</v>
-      </c>
-      <c r="K15" s="2">
-        <v>0.57299999999999995</v>
-      </c>
-      <c r="L15" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:14" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="B21" s="2">
-        <v>1044.8499999999999</v>
-      </c>
-      <c r="C21" s="2">
-        <v>5.4298000000000002</v>
-      </c>
-      <c r="D21" s="2">
-        <v>5.7060000000000004</v>
-      </c>
-      <c r="E21" s="2">
-        <v>5.1535000000000002</v>
-      </c>
-      <c r="F21" s="2">
-        <v>8.8309999999999995</v>
-      </c>
-      <c r="G21" s="3">
-        <v>7.6388999999999996</v>
-      </c>
-      <c r="H21" s="2">
-        <v>2.3407</v>
-      </c>
-      <c r="I21" s="2">
-        <v>2.0931000000000002</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0.43169999999999997</v>
-      </c>
-      <c r="K21" s="2">
-        <v>0.84689999999999999</v>
-      </c>
-      <c r="L21" s="2">
-        <v>0.57120000000000004</v>
-      </c>
-      <c r="M21" s="2">
-        <v>0.69359999999999999</v>
-      </c>
-      <c r="N21" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>120</v>
-      </c>
-      <c r="B46" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>122</v>
-      </c>
-      <c r="B47">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>117</v>
-      </c>
-      <c r="B48">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>123</v>
-      </c>
-      <c r="B49" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>125</v>
-      </c>
-      <c r="B50">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>126</v>
-      </c>
-      <c r="B51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>127</v>
-      </c>
-      <c r="B52" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>128</v>
-      </c>
-      <c r="B53" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>130</v>
-      </c>
-      <c r="B54">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>131</v>
-      </c>
-      <c r="B55">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>132</v>
-      </c>
-      <c r="B56">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>133</v>
-      </c>
-      <c r="B57">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>134</v>
-      </c>
-      <c r="B58">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>135</v>
-      </c>
-      <c r="B59">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>136</v>
-      </c>
-      <c r="B60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>137</v>
-      </c>
-      <c r="B61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>138</v>
-      </c>
-      <c r="B62" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>140</v>
-      </c>
-      <c r="B63">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>141</v>
-      </c>
-      <c r="B64" s="8">
-        <v>1.0000000000000001E-5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>142</v>
-      </c>
-      <c r="B65">
-        <v>0.38082122802734297</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>143</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>144</v>
-      </c>
-      <c r="B67">
-        <v>1.3335416992238299E-4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>145</v>
-      </c>
-      <c r="B68">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>146</v>
-      </c>
-      <c r="B69" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>148</v>
-      </c>
-      <c r="B70" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>151</v>
-      </c>
-      <c r="B72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>152</v>
-      </c>
-      <c r="B73" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -22698,7 +23242,7 @@
     </row>
     <row r="2" spans="1:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -22733,7 +23277,7 @@
     </row>
     <row r="3" spans="1:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B3" s="2">
         <v>7.31</v>
@@ -22767,8 +23311,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>18</v>
+      <c r="A4" t="s">
+        <v>201</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -22995,7 +23539,7 @@
         <v>146</v>
       </c>
       <c r="B60" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">

--- a/cnn results/cnn result - epsilon.xlsx
+++ b/cnn results/cnn result - epsilon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\flight delay\stpn paper\STPN-main\cnn results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC2A3EE-9B89-43F5-BCA4-4538660519C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611184E3-38A7-4453-AA0D-F5DEA6BABB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="731" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="731" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
@@ -882,16 +882,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>23.976868146043799</c:v>
+                  <c:v>1.9904279458387499</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>7.3646261980491197</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>14.9978621331353</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.3646261980491197</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9904279458387499</c:v>
+                  <c:v>23.976868146043799</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -903,16 +903,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>8.2672139664071604</c:v>
+                  <c:v>8.8102144397220403</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>8.7051407717552696</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>8.5147397498501007</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.7051407717552696</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.8102144397220403</c:v>
+                  <c:v>8.2672139664071604</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -994,16 +994,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>1.9904279458387499</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.3646261980491197</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.9978621331353</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>23.976868146043799</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>14.9978621331353</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>7.3646261980491197</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>1.9904279458387499</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1021,16 +1021,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>4.2813004793063696</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>4.3567055869653597</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>4.24443066860026</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>4.9284034311393201</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>4.24443066860026</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>4.3567055869653597</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>4.2813004793063696</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1101,16 +1101,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>1.9904279458387499</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.3646261980491197</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.9978621331353</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>23.976868146043799</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>14.9978621331353</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>7.3646261980491197</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>1.9904279458387499</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1128,16 +1128,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>5.3772165774258802</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>5.40894905246126</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5.27776901571651</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>5.7363358065724803</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>5.27776901571651</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>5.40894905246126</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>5.3772165774258802</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -1502,6 +1502,1325 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'time remove'!$H$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Arr_NonDel_MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'time remove'!$B$16:$B$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.9770000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.1420000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.068</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'time remove'!$H$16:$H$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.7050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.6660000000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.79</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.9589999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4B68-4346-B11A-74B252858581}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'time remove'!$I$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Dep_NonDel_MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'time remove'!$B$16:$B$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.9770000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.1420000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.068</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'time remove'!$I$16:$I$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.379</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.9049999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.3289999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.6619999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-4B68-4346-B11A-74B252858581}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="857918928"/>
+        <c:axId val="857918512"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="857918928"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="857918512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="857918512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="857918928"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'time seq len'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Overall_MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'time seq len'!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'time seq len'!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.6689999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.0620000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5339999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.5270000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D3CC-400F-82DE-02FA2E81A403}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'time seq len'!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Arr_NonDel_MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'time seq len'!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'time seq len'!$H$2:$H$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.8019999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5590000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9589999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.0529999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-D3CC-400F-82DE-02FA2E81A403}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'time seq len'!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Dep_NonDel_MAE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'time seq len'!$A$2:$A$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'time seq len'!$I$2:$I$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.8579999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.4160000000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.6619999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.6399999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-D3CC-400F-82DE-02FA2E81A403}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="622478528"/>
+        <c:axId val="622499744"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$D$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Arr_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>24</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$D$2:$D$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>7.0490000000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>6.1929999999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5.702</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5.7480000000000002</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-D3CC-400F-82DE-02FA2E81A403}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$E$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Dep_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>24</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$E$2:$E$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>6.2889999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>5.93</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5.367</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5.306</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-D3CC-400F-82DE-02FA2E81A403}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$F$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Arr_Del_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>24</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$F$2:$F$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>7.7350000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.96</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>7.7709999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>7.6840000000000002</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-D3CC-400F-82DE-02FA2E81A403}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$G$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Dep_Del_MAE</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>24</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'time seq len'!$G$2:$G$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>7.8159999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.7510000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>7.8609999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>7.6619999999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-D3CC-400F-82DE-02FA2E81A403}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="622478528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="622499744"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="622499744"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="4"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="622478528"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
     <c:title>
       <c:overlay val="0"/>
       <c:spPr>
@@ -1750,7 +3069,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$E$13</c15:sqref>
@@ -1791,7 +3110,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
@@ -1818,7 +3137,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$E$14:$E$17</c15:sqref>
@@ -1857,7 +3176,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$F$13</c15:sqref>
@@ -1898,7 +3217,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
@@ -1925,7 +3244,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$F$14:$F$17</c15:sqref>
@@ -1964,7 +3283,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$H$13</c15:sqref>
@@ -2005,7 +3324,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
@@ -2032,7 +3351,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$H$14:$H$17</c15:sqref>
@@ -2071,7 +3390,7 @@
                 <c:order val="5"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$I$13</c15:sqref>
@@ -2112,7 +3431,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
@@ -2139,7 +3458,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$I$14:$I$17</c15:sqref>
@@ -2178,7 +3497,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$J$13</c15:sqref>
@@ -2225,7 +3544,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
@@ -2252,7 +3571,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$J$14:$J$17</c15:sqref>
@@ -2495,7 +3814,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2757,7 +4076,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$F$13</c15:sqref>
@@ -2798,7 +4117,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
@@ -2825,7 +4144,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$F$14:$F$17</c15:sqref>
@@ -2864,7 +4183,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$G$13</c15:sqref>
@@ -2905,7 +4224,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
@@ -2932,7 +4251,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$G$14:$G$17</c15:sqref>
@@ -2971,7 +4290,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$H$13</c15:sqref>
@@ -3012,7 +4331,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
@@ -3039,7 +4358,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$H$14:$H$17</c15:sqref>
@@ -3078,7 +4397,7 @@
                 <c:order val="5"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$I$13</c15:sqref>
@@ -3119,7 +4438,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
@@ -3146,7 +4465,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$I$14:$I$17</c15:sqref>
@@ -3185,7 +4504,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$J$13</c15:sqref>
@@ -3232,7 +4551,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$A$14:$A$17</c15:sqref>
@@ -3259,7 +4578,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time seq len'!$J$14:$J$17</c15:sqref>
@@ -3502,7 +4821,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3857,7 +5176,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4473,7 +5792,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4924,16 +6243,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>23.976868146043799</c:v>
+                  <c:v>1.9904279458387499</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>7.3646261980491197</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>14.9978621331353</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.3646261980491197</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9904279458387499</c:v>
+                  <c:v>23.976868146043799</c:v>
                 </c:pt>
               </c:numCache>
               <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
@@ -4946,16 +6265,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.9284034311393201</c:v>
+                  <c:v>4.2813004793063696</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>4.3567055869653597</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>4.24443066860026</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.3567055869653597</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.2813004793063696</c:v>
+                  <c:v>4.9284034311393201</c:v>
                 </c:pt>
               </c:numCache>
               <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
@@ -5038,16 +6357,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>1.9904279458387499</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.3646261980491197</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.9978621331353</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>23.976868146043799</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>14.9978621331353</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>7.3646261980491197</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>1.9904279458387499</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5065,16 +6384,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>8.8102144397220403</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8.7051407717552696</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>8.5147397498501007</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>8.2672139664071604</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>8.5147397498501007</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>8.7051407717552696</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>8.8102144397220403</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5145,16 +6464,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>1.9904279458387499</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.3646261980491197</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.9978621331353</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>23.976868146043799</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>14.9978621331353</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>7.3646261980491197</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>1.9904279458387499</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5172,16 +6491,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>5.3772165774258802</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>5.40894905246126</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5.27776901571651</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>5.7363358065724803</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>5.27776901571651</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>5.40894905246126</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>5.3772165774258802</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5500,16 +6819,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>23.976868146043799</c:v>
+                  <c:v>1.9904279458387499</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>7.3646261980491197</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>14.9978621331353</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.3646261980491197</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9904279458387499</c:v>
+                  <c:v>23.976868146043799</c:v>
                 </c:pt>
               </c:numCache>
               <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
@@ -5522,16 +6841,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.7363358065724803</c:v>
+                  <c:v>5.3772165774258802</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>5.40894905246126</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>5.27776901571651</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.40894905246126</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.3772165774258802</c:v>
+                  <c:v>5.7363358065724803</c:v>
                 </c:pt>
               </c:numCache>
               <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
@@ -5614,16 +6933,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>1.9904279458387499</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.3646261980491197</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.9978621331353</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>23.976868146043799</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>14.9978621331353</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>7.3646261980491197</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>1.9904279458387499</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5641,16 +6960,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>8.8102144397220403</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8.7051407717552696</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>8.5147397498501007</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>8.2672139664071604</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>8.5147397498501007</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>8.7051407717552696</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>8.8102144397220403</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5721,16 +7040,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>1.9904279458387499</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.3646261980491197</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.9978621331353</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>23.976868146043799</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>14.9978621331353</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>7.3646261980491197</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>1.9904279458387499</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -5748,16 +7067,16 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="4"/>
                       <c:pt idx="0">
+                        <c:v>4.2813004793063696</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>4.3567055869653597</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>4.24443066860026</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
                         <c:v>4.9284034311393201</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>4.24443066860026</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>4.3567055869653597</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>4.2813004793063696</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -9021,6 +10340,487 @@
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'delay threshold'!$V$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Arr MAE Delayed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'delay threshold'!$Q$2:$Q$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'delay threshold'!$V$2:$V$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>8.5147397498501007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.9765999999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.8507999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7210-4DAD-8499-281278DAA02A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'delay threshold'!$W$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Dep MAE Delayed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'delay threshold'!$Q$2:$Q$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'delay threshold'!$W$2:$W$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>8.5147397498501007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.5744000000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.892099999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-7210-4DAD-8499-281278DAA02A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'delay threshold'!$X$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Arr MAE Non-delayed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'delay threshold'!$Q$2:$Q$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'delay threshold'!$X$2:$X$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4.24443066860026</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.2497999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.3421000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-7210-4DAD-8499-281278DAA02A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="386799168"/>
+        <c:axId val="386775456"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="386799168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="386775456"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="386775456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="386799168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
@@ -9063,7 +10863,7 @@
               <c:f>'time remove'!$B$16:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1.9770000000000001</c:v>
                 </c:pt>
@@ -9073,9 +10873,6 @@
                 <c:pt idx="2">
                   <c:v>14.068</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>23.295999999999999</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -9084,7 +10881,7 @@
               <c:f>'time remove'!$F$16:$F$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>8.6910000000000007</c:v>
                 </c:pt>
@@ -9093,9 +10890,6 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>7.9370000000000003</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.0540000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9148,7 +10942,7 @@
               <c:f>'time remove'!$B$16:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1.9770000000000001</c:v>
                 </c:pt>
@@ -9157,9 +10951,6 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>14.068</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23.295999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9260,7 +11051,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>1.9770000000000001</c:v>
                       </c:pt>
@@ -9269,9 +11060,6 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>14.068</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>23.295999999999999</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -9287,7 +11075,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>4.7869999999999999</c:v>
                       </c:pt>
@@ -9296,9 +11084,6 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>5.3769999999999998</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>5.2320000000000002</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -9317,7 +11102,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$D$15</c15:sqref>
@@ -9358,7 +11143,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
@@ -9367,7 +11152,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>1.9770000000000001</c:v>
                       </c:pt>
@@ -9376,16 +11161,13 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>14.068</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>23.295999999999999</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$D$16:$D$19</c15:sqref>
@@ -9394,7 +11176,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>5.0030000000000001</c:v>
                       </c:pt>
@@ -9403,15 +11185,12 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>5.609</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>5.4080000000000004</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-10FD-491C-BBA9-FC4699357C98}"/>
                   </c:ext>
@@ -9424,7 +11203,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$E$15</c15:sqref>
@@ -9465,7 +11244,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
@@ -9474,7 +11253,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>1.9770000000000001</c:v>
                       </c:pt>
@@ -9483,16 +11262,13 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>14.068</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>23.295999999999999</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$E$16:$E$19</c15:sqref>
@@ -9501,7 +11277,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>4.5709999999999997</c:v>
                       </c:pt>
@@ -9510,15 +11286,12 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>5.1440000000000001</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>5.0570000000000004</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-10FD-491C-BBA9-FC4699357C98}"/>
                   </c:ext>
@@ -9531,7 +11304,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$G$15</c15:sqref>
@@ -9572,7 +11345,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
@@ -9581,7 +11354,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>1.9770000000000001</c:v>
                       </c:pt>
@@ -9590,16 +11363,13 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>14.068</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>23.295999999999999</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$G$16:$G$19</c15:sqref>
@@ -9608,7 +11378,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>8.8789999999999996</c:v>
                       </c:pt>
@@ -9617,15 +11387,12 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>8.093</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>8.1319999999999997</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000005-10FD-491C-BBA9-FC4699357C98}"/>
                   </c:ext>
@@ -9638,7 +11405,7 @@
                 <c:order val="5"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$H$15</c15:sqref>
@@ -9679,7 +11446,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
@@ -9688,7 +11455,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>1.9770000000000001</c:v>
                       </c:pt>
@@ -9697,16 +11464,13 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>14.068</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>23.295999999999999</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$H$16:$H$19</c15:sqref>
@@ -9715,7 +11479,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>3.7050000000000001</c:v>
                       </c:pt>
@@ -9724,15 +11488,12 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>4.79</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>4.4770000000000003</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000006-10FD-491C-BBA9-FC4699357C98}"/>
                   </c:ext>
@@ -9745,7 +11506,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$I$15</c15:sqref>
@@ -9792,7 +11553,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$B$16:$B$19</c15:sqref>
@@ -9801,7 +11562,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>1.9770000000000001</c:v>
                       </c:pt>
@@ -9810,16 +11571,13 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>14.068</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>23.295999999999999</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'time remove'!$I$16:$I$19</c15:sqref>
@@ -9828,7 +11586,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>3.379</c:v>
                       </c:pt>
@@ -9837,15 +11595,12 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>4.3289999999999997</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>4.2060000000000004</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000007-10FD-491C-BBA9-FC4699357C98}"/>
                   </c:ext>
@@ -9914,7 +11669,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>1.9770000000000001</c:v>
                       </c:pt>
@@ -9923,9 +11678,6 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>14.068</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>23.295999999999999</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -9941,7 +11693,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>0.76900000000000002</c:v>
                       </c:pt>
@@ -9950,9 +11702,6 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0.74199999999999999</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>0.747</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -10027,7 +11776,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>1.9770000000000001</c:v>
                       </c:pt>
@@ -10036,9 +11785,6 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>14.068</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>23.295999999999999</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -10054,7 +11800,7 @@
                     </c:extLst>
                     <c:numCache>
                       <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
+                      <c:ptCount val="3"/>
                       <c:pt idx="0">
                         <c:v>0.56999999999999995</c:v>
                       </c:pt>
@@ -10063,9 +11809,6 @@
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>0.58499999999999996</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>0.57599999999999996</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
@@ -10203,944 +11946,6 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="111502607"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'time seq len'!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Overall_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'time seq len'!$A$2:$A$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>24</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'time seq len'!$C$2:$C$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>6.6689999999999996</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.0620000000000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.5339999999999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.5270000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D3CC-400F-82DE-02FA2E81A403}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'time seq len'!$H$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Arr_NonDel_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'time seq len'!$A$2:$A$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>24</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'time seq len'!$H$2:$H$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>6.8019999999999996</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.5590000000000002</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.9589999999999996</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.0529999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-D3CC-400F-82DE-02FA2E81A403}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'time seq len'!$I$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Dep_NonDel_MAE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'time seq len'!$A$2:$A$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>24</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'time seq len'!$I$2:$I$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>5.8579999999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.4160000000000004</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.6619999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.6399999999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-D3CC-400F-82DE-02FA2E81A403}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="622478528"/>
-        <c:axId val="622499744"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredScatterSeries>
-              <c15:ser>
-                <c:idx val="1"/>
-                <c:order val="1"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$D$1</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>Arr_MAE</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="19050" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent2"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="5"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent2"/>
-                    </a:solidFill>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent2"/>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:xVal>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
-                        <c:v>8</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>12</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>18</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>24</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:xVal>
-                <c:yVal>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$D$2:$D$5</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
-                        <c:v>7.0490000000000004</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>6.1929999999999996</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>5.702</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>5.7480000000000002</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:yVal>
-                <c:smooth val="1"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000001-D3CC-400F-82DE-02FA2E81A403}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredScatterSeries>
-            <c15:filteredScatterSeries>
-              <c15:ser>
-                <c:idx val="2"/>
-                <c:order val="2"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$E$1</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>Dep_MAE</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="19050" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent3"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="5"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent3"/>
-                    </a:solidFill>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent3"/>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:xVal>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
-                        <c:v>8</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>12</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>18</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>24</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:xVal>
-                <c:yVal>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$E$2:$E$5</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
-                        <c:v>6.2889999999999997</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>5.93</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>5.367</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>5.306</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:yVal>
-                <c:smooth val="1"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000002-D3CC-400F-82DE-02FA2E81A403}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredScatterSeries>
-            <c15:filteredScatterSeries>
-              <c15:ser>
-                <c:idx val="3"/>
-                <c:order val="3"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$F$1</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>Arr_Del_MAE</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="19050" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent4"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="5"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent4"/>
-                    </a:solidFill>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent4"/>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:xVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
-                        <c:v>8</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>12</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>18</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>24</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:xVal>
-                <c:yVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$F$2:$F$5</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
-                        <c:v>7.7350000000000003</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>7.96</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>7.7709999999999999</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>7.6840000000000002</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:yVal>
-                <c:smooth val="1"/>
-                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000003-D3CC-400F-82DE-02FA2E81A403}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredScatterSeries>
-            <c15:filteredScatterSeries>
-              <c15:ser>
-                <c:idx val="4"/>
-                <c:order val="4"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$G$1</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>Dep_Del_MAE</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="19050" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent5"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="5"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent5"/>
-                    </a:solidFill>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="accent5"/>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:xVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$A$2:$A$5</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
-                        <c:v>8</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>12</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>18</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>24</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:xVal>
-                <c:yVal>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'time seq len'!$G$2:$G$5</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
-                        <c:v>7.8159999999999998</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>7.7510000000000003</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>7.8609999999999998</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>7.6619999999999999</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:yVal>
-                <c:smooth val="1"/>
-                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000005-D3CC-400F-82DE-02FA2E81A403}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredScatterSeries>
-          </c:ext>
-        </c:extLst>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="622478528"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="622499744"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="622499744"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="4"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="622478528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -11428,6 +12233,86 @@
 </file>
 
 <file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -14883,6 +15768,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -19170,16 +21087,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>125730</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>163454</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>466329</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>7545</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -19283,6 +21200,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>792480</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>434340</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86F1682E-A97B-4EBB-9E9A-69C0C2295C80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -19319,6 +21272,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>319218</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>275968</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>370704</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>43249</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89A722D9-F495-46A3-90DC-C1893EF23A19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -19821,9 +21810,10 @@
   <dimension ref="A1:W141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" customWidth="1"/>
     <col min="2" max="2" width="11.109375" style="4" customWidth="1"/>
-    <col min="3" max="4" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
     <col min="5" max="8" width="8.88671875" customWidth="1"/>
     <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.88671875" customWidth="1"/>
@@ -19906,55 +21896,55 @@
     </row>
     <row r="2" spans="1:23" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>23.976868146043799</v>
+        <v>1.9904279458387499</v>
       </c>
       <c r="C2" s="2">
-        <v>0.70924004384359796</v>
+        <v>0.72177201315306005</v>
       </c>
       <c r="D2" s="2">
-        <v>0.55353798523042896</v>
+        <v>0.54272390851380203</v>
       </c>
       <c r="E2" s="2">
-        <v>8.2672139664071604</v>
+        <v>8.8102144397220403</v>
       </c>
       <c r="F2" s="2">
-        <v>4.9284034311393201</v>
+        <v>4.2813004793063696</v>
       </c>
       <c r="G2" s="2">
-        <v>5.7363358065724803</v>
+        <v>5.3772165774258802</v>
       </c>
       <c r="H2" s="2">
-        <v>10.682204212591399</v>
+        <v>11.359580368952599</v>
       </c>
       <c r="I2" s="2">
-        <v>6.4610741300721699</v>
+        <v>5.7524061854957198</v>
       </c>
       <c r="J2" s="2">
-        <v>7.6978096438446304</v>
+        <v>7.5038878153282198</v>
       </c>
       <c r="K2" s="2">
-        <v>4963.8773679733204</v>
+        <v>6572.8929276466297</v>
       </c>
       <c r="L2" s="2">
-        <v>1394.84722948074</v>
+        <v>1253.7568855285599</v>
       </c>
       <c r="M2" s="2">
-        <v>1845.10709166526</v>
+        <v>1516.5282146930599</v>
       </c>
       <c r="N2" s="2">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="O2" s="2">
         <v>5474</v>
       </c>
       <c r="P2" s="2">
-        <v>136.73052815198801</v>
+        <v>155.71963379780399</v>
       </c>
       <c r="Q2" s="2">
-        <v>8203.8316891193299</v>
+        <v>9343.1780278682709</v>
       </c>
       <c r="R2" s="2">
         <v>19207</v>
@@ -19977,55 +21967,55 @@
     </row>
     <row r="3" spans="1:23" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
-        <v>14.9978621331353</v>
+        <v>7.3646261980491197</v>
       </c>
       <c r="C3" s="2">
-        <v>0.73337230544388898</v>
+        <v>0.72259408111067802</v>
       </c>
       <c r="D3" s="2">
-        <v>0.55983800164434405</v>
+        <v>0.54226424862108402</v>
       </c>
       <c r="E3" s="2">
-        <v>8.5147397498501007</v>
+        <v>8.7051407717552696</v>
       </c>
       <c r="F3" s="2">
-        <v>4.24443066860026</v>
+        <v>4.3567055869653597</v>
       </c>
       <c r="G3" s="2">
-        <v>5.27776901571651</v>
+        <v>5.40894905246126</v>
       </c>
       <c r="H3" s="2">
-        <v>10.9943399425701</v>
+        <v>11.203591800959</v>
       </c>
       <c r="I3" s="2">
-        <v>5.9242952205638799</v>
+        <v>6.0297271615041899</v>
       </c>
       <c r="J3" s="2">
-        <v>7.4735581566905296</v>
+        <v>7.6114010142308297</v>
       </c>
       <c r="K3" s="2">
-        <v>6583.5351414680399</v>
+        <v>5059.42527604103</v>
       </c>
       <c r="L3" s="2">
-        <v>1269.01271510124</v>
+        <v>1422.63944673538</v>
       </c>
       <c r="M3" s="2">
-        <v>1498.7497563362101</v>
+        <v>1966.33158445358</v>
       </c>
       <c r="N3" s="2">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="O3" s="2">
         <v>5474</v>
       </c>
       <c r="P3" s="2">
-        <v>155.85496021509101</v>
+        <v>140.806605120499</v>
       </c>
       <c r="Q3" s="2">
-        <v>9351.2976129055005</v>
+        <v>8448.3963072299903</v>
       </c>
       <c r="R3" s="2">
         <v>19207</v>
@@ -20048,55 +22038,55 @@
     </row>
     <row r="4" spans="1:23" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3">
-        <v>7.3646261980491197</v>
+        <v>14.9978621331353</v>
       </c>
       <c r="C4" s="2">
-        <v>0.72259408111067802</v>
+        <v>0.73337230544388898</v>
       </c>
       <c r="D4" s="2">
-        <v>0.54226424862108402</v>
+        <v>0.55983800164434405</v>
       </c>
       <c r="E4" s="2">
-        <v>8.7051407717552696</v>
+        <v>8.5147397498501007</v>
       </c>
       <c r="F4" s="2">
-        <v>4.3567055869653597</v>
+        <v>4.24443066860026</v>
       </c>
       <c r="G4" s="2">
-        <v>5.40894905246126</v>
+        <v>5.27776901571651</v>
       </c>
       <c r="H4" s="2">
-        <v>11.203591800959</v>
+        <v>10.9943399425701</v>
       </c>
       <c r="I4" s="2">
-        <v>6.0297271615041899</v>
+        <v>5.9242952205638799</v>
       </c>
       <c r="J4" s="2">
-        <v>7.6114010142308297</v>
+        <v>7.4735581566905296</v>
       </c>
       <c r="K4" s="2">
-        <v>5059.42527604103</v>
+        <v>6583.5351414680399</v>
       </c>
       <c r="L4" s="2">
-        <v>1422.63944673538</v>
+        <v>1269.01271510124</v>
       </c>
       <c r="M4" s="2">
-        <v>1966.33158445358</v>
+        <v>1498.7497563362101</v>
       </c>
       <c r="N4" s="2">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="O4" s="2">
         <v>5474</v>
       </c>
       <c r="P4" s="2">
-        <v>140.806605120499</v>
+        <v>155.85496021509101</v>
       </c>
       <c r="Q4" s="2">
-        <v>8448.3963072299903</v>
+        <v>9351.2976129055005</v>
       </c>
       <c r="R4" s="2">
         <v>19207</v>
@@ -20119,55 +22109,55 @@
     </row>
     <row r="5" spans="1:23" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3">
+        <v>23.976868146043799</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.70924004384359796</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.55353798523042896</v>
+      </c>
+      <c r="E5" s="2">
+        <v>8.2672139664071604</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4.9284034311393201</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5.7363358065724803</v>
+      </c>
+      <c r="H5" s="2">
+        <v>10.682204212591399</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.4610741300721699</v>
+      </c>
+      <c r="J5" s="2">
+        <v>7.6978096438446304</v>
+      </c>
+      <c r="K5" s="2">
+        <v>4963.8773679733204</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1394.84722948074</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1845.10709166526</v>
+      </c>
+      <c r="N5" s="2">
         <v>25</v>
-      </c>
-      <c r="B5" s="3">
-        <v>1.9904279458387499</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.72177201315306005</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.54272390851380203</v>
-      </c>
-      <c r="E5" s="2">
-        <v>8.8102144397220403</v>
-      </c>
-      <c r="F5" s="2">
-        <v>4.2813004793063696</v>
-      </c>
-      <c r="G5" s="2">
-        <v>5.3772165774258802</v>
-      </c>
-      <c r="H5" s="2">
-        <v>11.359580368952599</v>
-      </c>
-      <c r="I5" s="2">
-        <v>5.7524061854957198</v>
-      </c>
-      <c r="J5" s="2">
-        <v>7.5038878153282198</v>
-      </c>
-      <c r="K5" s="2">
-        <v>6572.8929276466297</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1253.7568855285599</v>
-      </c>
-      <c r="M5" s="2">
-        <v>1516.5282146930599</v>
-      </c>
-      <c r="N5" s="2">
-        <v>2</v>
       </c>
       <c r="O5" s="2">
         <v>5474</v>
       </c>
       <c r="P5" s="2">
-        <v>155.71963379780399</v>
+        <v>136.73052815198801</v>
       </c>
       <c r="Q5" s="2">
-        <v>9343.1780278682709</v>
+        <v>8203.8316891193299</v>
       </c>
       <c r="R5" s="2">
         <v>19207</v>
@@ -20816,6 +22806,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R5">
+    <sortCondition ref="B2:B5"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -22569,6 +24562,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABFDE7E-B98D-4DEB-8254-0F537CE2C12A}">
   <dimension ref="A1:L60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="12.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -22894,7 +24890,7 @@
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>5</v>
       </c>
